--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128674395</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>128674334</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128674395</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>128674334</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128674395</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>128674334</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128674395</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>128674334</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128674395</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>128674334</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128674395</v>
       </c>
       <c r="B3" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>128674334</v>
       </c>
       <c r="B4" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128674395</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>128674334</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>128674395</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>128674334</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -996,6 +996,4230 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129543469</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96166</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>210</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>571323</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6465679</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129543544</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>571456</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6465730</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129543327</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>571291</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6465665</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129543430</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>571367</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6465787</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129543448</v>
+      </c>
+      <c r="B9" t="n">
+        <v>4773</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>571395</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6465767</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129543522</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>571382</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6465758</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129543463</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79663</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>571341</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6465672</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129543434</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91550</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>571376</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6465781</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129543553</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91564</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>571453</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6465695</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129543516</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>571375</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6465752</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ett tiotal</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129543475</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>571318</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6465687</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129543571</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91550</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>571390</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6465679</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129543676</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91550</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>571480</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6465733</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129543392</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>571309</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6465740</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129543383</v>
+      </c>
+      <c r="B19" t="n">
+        <v>105790</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>571325</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6465727</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ett tjugotal</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129543452</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92192</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5454</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Hornvaxskinn</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Crustoderma corneum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>571381</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6465712</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129543658</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91550</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>571408</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6465658</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129543526</v>
+      </c>
+      <c r="B22" t="n">
+        <v>105790</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>571437</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6465763</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ett tiotal</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129543484</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>571327</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6465739</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129543348</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>571288</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6465690</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129543378</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>571325</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6465727</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129543457</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91550</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>571370</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6465725</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129543509</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92003</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>571359</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6465750</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129543603</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>571376</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6465679</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129543537</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>571452</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6465730</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129543344</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>571283</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6465682</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129543678</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>571480</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6465780</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129543655</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79663</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>571375</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6465649</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129543442</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>571390</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6465781</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129543686</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>571437</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6465801</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129543389</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>571323</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6465742</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ett tjugotal</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129543685</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>571461</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6465806</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129543368</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>571324</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6465733</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129543564</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91550</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>571443</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6465681</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129543361</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>571328</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6465727</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129543356</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>571315</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6465727</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129543624</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>571370</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6465662</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ett tiotal</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129543651</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79663</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>571336</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6465638</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129543662</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91550</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>571429</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6465708</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129543395</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>571344</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6465783</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ett tiotal</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>129543469</v>
       </c>
       <c r="B5" t="n">
-        <v>96166</v>
+        <v>96169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543544</v>
+        <v>129543327</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571456</v>
+        <v>571291</v>
       </c>
       <c r="R6" t="n">
-        <v>6465730</v>
+        <v>6465665</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543327</v>
+        <v>129543544</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571291</v>
+        <v>571456</v>
       </c>
       <c r="R7" t="n">
-        <v>6465665</v>
+        <v>6465730</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,38 +1314,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543430</v>
+        <v>129543463</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>79663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1353,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571367</v>
+        <v>571341</v>
       </c>
       <c r="R8" t="n">
-        <v>6465787</v>
+        <v>6465672</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1527,7 +1521,7 @@
         <v>129543522</v>
       </c>
       <c r="B10" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,37 +1625,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543463</v>
+        <v>129543430</v>
       </c>
       <c r="B11" t="n">
-        <v>79663</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1669,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571341</v>
+        <v>571367</v>
       </c>
       <c r="R11" t="n">
-        <v>6465672</v>
+        <v>6465787</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,6 +1700,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1732,10 +1732,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129543434</v>
+        <v>129543553</v>
       </c>
       <c r="B12" t="n">
-        <v>91550</v>
+        <v>91567</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1743,21 +1743,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571376</v>
+        <v>571453</v>
       </c>
       <c r="R12" t="n">
-        <v>6465781</v>
+        <v>6465695</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129543553</v>
+        <v>129543434</v>
       </c>
       <c r="B13" t="n">
-        <v>91564</v>
+        <v>91553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,21 +1844,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571453</v>
+        <v>571376</v>
       </c>
       <c r="R13" t="n">
-        <v>6465695</v>
+        <v>6465781</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,7 +1937,7 @@
         <v>129543516</v>
       </c>
       <c r="B14" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>129543475</v>
       </c>
       <c r="B15" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>129543571</v>
       </c>
       <c r="B16" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2249,10 +2249,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543676</v>
+        <v>129543452</v>
       </c>
       <c r="B17" t="n">
-        <v>91550</v>
+        <v>92195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2260,21 +2260,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5454</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571480</v>
+        <v>571381</v>
       </c>
       <c r="R17" t="n">
-        <v>6465733</v>
+        <v>6465712</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,38 +2350,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543392</v>
+        <v>129543676</v>
       </c>
       <c r="B18" t="n">
-        <v>98724</v>
+        <v>91553</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2389,10 +2388,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571309</v>
+        <v>571480</v>
       </c>
       <c r="R18" t="n">
-        <v>6465740</v>
+        <v>6465733</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2425,11 +2424,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2460,7 +2454,7 @@
         <v>129543383</v>
       </c>
       <c r="B19" t="n">
-        <v>105790</v>
+        <v>105793</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2564,37 +2558,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129543452</v>
+        <v>129543392</v>
       </c>
       <c r="B20" t="n">
-        <v>92192</v>
+        <v>98727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5454</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2602,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571381</v>
+        <v>571309</v>
       </c>
       <c r="R20" t="n">
-        <v>6465712</v>
+        <v>6465740</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,6 +2633,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2668,7 +2668,7 @@
         <v>129543658</v>
       </c>
       <c r="B21" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129543526</v>
       </c>
       <c r="B22" t="n">
-        <v>105790</v>
+        <v>105793</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2873,38 +2873,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129543484</v>
+        <v>129543457</v>
       </c>
       <c r="B23" t="n">
-        <v>98724</v>
+        <v>91553</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2912,10 +2911,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571327</v>
+        <v>571370</v>
       </c>
       <c r="R23" t="n">
-        <v>6465739</v>
+        <v>6465725</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,11 +2947,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2980,10 +2974,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129543348</v>
+        <v>129543484</v>
       </c>
       <c r="B24" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3019,10 +3013,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571288</v>
+        <v>571327</v>
       </c>
       <c r="R24" t="n">
-        <v>6465690</v>
+        <v>6465739</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3087,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543378</v>
+        <v>129543348</v>
       </c>
       <c r="B25" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3126,10 +3120,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571325</v>
+        <v>571288</v>
       </c>
       <c r="R25" t="n">
-        <v>6465727</v>
+        <v>6465690</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3194,37 +3188,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129543457</v>
+        <v>129543378</v>
       </c>
       <c r="B26" t="n">
-        <v>91550</v>
+        <v>98727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3232,10 +3227,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571370</v>
+        <v>571325</v>
       </c>
       <c r="R26" t="n">
-        <v>6465725</v>
+        <v>6465727</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3268,6 +3263,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3295,37 +3295,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543509</v>
+        <v>129543603</v>
       </c>
       <c r="B27" t="n">
-        <v>92003</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3333,10 +3346,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571359</v>
+        <v>571376</v>
       </c>
       <c r="R27" t="n">
-        <v>6465750</v>
+        <v>6465679</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3373,7 +3386,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
+          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3382,7 +3395,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3401,50 +3413,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543603</v>
+        <v>129543537</v>
       </c>
       <c r="B28" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3452,10 +3452,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571376</v>
+        <v>571452</v>
       </c>
       <c r="R28" t="n">
-        <v>6465679</v>
+        <v>6465730</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3501,6 +3501,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3519,10 +3520,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543537</v>
+        <v>129543509</v>
       </c>
       <c r="B29" t="n">
-        <v>98724</v>
+        <v>92006</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3530,27 +3531,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571452</v>
+        <v>571359</v>
       </c>
       <c r="R29" t="n">
-        <v>6465730</v>
+        <v>6465750</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3751,7 +3751,7 @@
         <v>129543678</v>
       </c>
       <c r="B31" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3855,37 +3855,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543655</v>
+        <v>129543442</v>
       </c>
       <c r="B32" t="n">
-        <v>79663</v>
+        <v>98727</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3893,10 +3894,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571375</v>
+        <v>571390</v>
       </c>
       <c r="R32" t="n">
-        <v>6465649</v>
+        <v>6465781</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3929,6 +3930,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3956,38 +3962,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543442</v>
+        <v>129543655</v>
       </c>
       <c r="B33" t="n">
-        <v>98724</v>
+        <v>79663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3995,10 +4000,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571390</v>
+        <v>571375</v>
       </c>
       <c r="R33" t="n">
-        <v>6465781</v>
+        <v>6465649</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4031,11 +4036,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4066,7 +4066,7 @@
         <v>129543686</v>
       </c>
       <c r="B34" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,10 +4170,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543389</v>
+        <v>129543685</v>
       </c>
       <c r="B35" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>571323</v>
+        <v>571461</v>
       </c>
       <c r="R35" t="n">
-        <v>6465742</v>
+        <v>6465806</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ett tjugotal</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4277,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129543685</v>
+        <v>129543389</v>
       </c>
       <c r="B36" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>571461</v>
+        <v>571323</v>
       </c>
       <c r="R36" t="n">
-        <v>6465806</v>
+        <v>6465742</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4387,7 +4387,7 @@
         <v>129543368</v>
       </c>
       <c r="B37" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>129543564</v>
       </c>
       <c r="B38" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4592,10 +4592,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543361</v>
+        <v>129543356</v>
       </c>
       <c r="B39" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571328</v>
+        <v>571315</v>
       </c>
       <c r="R39" t="n">
         <v>6465727</v>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543356</v>
+        <v>129543361</v>
       </c>
       <c r="B40" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571315</v>
+        <v>571328</v>
       </c>
       <c r="R40" t="n">
         <v>6465727</v>
@@ -4809,7 +4809,7 @@
         <v>129543624</v>
       </c>
       <c r="B41" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>129543662</v>
       </c>
       <c r="B43" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>129543395</v>
       </c>
       <c r="B44" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -1314,37 +1314,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543463</v>
+        <v>129543430</v>
       </c>
       <c r="B8" t="n">
-        <v>79663</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1352,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571341</v>
+        <v>571367</v>
       </c>
       <c r="R8" t="n">
-        <v>6465672</v>
+        <v>6465787</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1389,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,39 +1421,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543448</v>
+        <v>129543522</v>
       </c>
       <c r="B9" t="n">
-        <v>4773</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1455,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571395</v>
+        <v>571382</v>
       </c>
       <c r="R9" t="n">
-        <v>6465767</v>
+        <v>6465758</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,6 +1496,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1518,38 +1528,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129543522</v>
+        <v>129543463</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>79663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1557,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571382</v>
+        <v>571341</v>
       </c>
       <c r="R10" t="n">
-        <v>6465758</v>
+        <v>6465672</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1625,38 +1629,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543430</v>
+        <v>129543448</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>4773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1664,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571367</v>
+        <v>571395</v>
       </c>
       <c r="R11" t="n">
-        <v>6465787</v>
+        <v>6465767</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,11 +1705,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2249,10 +2249,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543452</v>
+        <v>129543676</v>
       </c>
       <c r="B17" t="n">
-        <v>92195</v>
+        <v>91553</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2260,21 +2260,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5454</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571381</v>
+        <v>571480</v>
       </c>
       <c r="R17" t="n">
-        <v>6465712</v>
+        <v>6465733</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543676</v>
+        <v>129543452</v>
       </c>
       <c r="B18" t="n">
-        <v>91553</v>
+        <v>92195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,21 +2361,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5454</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571480</v>
+        <v>571381</v>
       </c>
       <c r="R18" t="n">
-        <v>6465733</v>
+        <v>6465712</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2451,32 +2451,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129543383</v>
+        <v>129543392</v>
       </c>
       <c r="B19" t="n">
-        <v>105793</v>
+        <v>98727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2490,10 +2490,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571325</v>
+        <v>571309</v>
       </c>
       <c r="R19" t="n">
-        <v>6465727</v>
+        <v>6465740</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ett tjugotal</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2558,32 +2558,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129543392</v>
+        <v>129543383</v>
       </c>
       <c r="B20" t="n">
-        <v>98727</v>
+        <v>105793</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571309</v>
+        <v>571325</v>
       </c>
       <c r="R20" t="n">
-        <v>6465740</v>
+        <v>6465727</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2873,37 +2873,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129543457</v>
+        <v>129543484</v>
       </c>
       <c r="B23" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2911,10 +2912,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571370</v>
+        <v>571327</v>
       </c>
       <c r="R23" t="n">
-        <v>6465725</v>
+        <v>6465739</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2947,6 +2948,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2974,7 +2980,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129543484</v>
+        <v>129543348</v>
       </c>
       <c r="B24" t="n">
         <v>98727</v>
@@ -3013,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571327</v>
+        <v>571288</v>
       </c>
       <c r="R24" t="n">
-        <v>6465739</v>
+        <v>6465690</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,7 +3087,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543348</v>
+        <v>129543378</v>
       </c>
       <c r="B25" t="n">
         <v>98727</v>
@@ -3120,10 +3126,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571288</v>
+        <v>571325</v>
       </c>
       <c r="R25" t="n">
-        <v>6465690</v>
+        <v>6465727</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3188,38 +3194,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129543378</v>
+        <v>129543457</v>
       </c>
       <c r="B26" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3227,10 +3232,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571325</v>
+        <v>571370</v>
       </c>
       <c r="R26" t="n">
-        <v>6465727</v>
+        <v>6465725</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3263,11 +3268,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3295,50 +3295,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543603</v>
+        <v>129543509</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>92006</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3346,10 +3333,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571376</v>
+        <v>571359</v>
       </c>
       <c r="R27" t="n">
-        <v>6465679</v>
+        <v>6465750</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3386,7 +3373,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
+          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3395,6 +3382,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3413,38 +3401,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543537</v>
+        <v>129543344</v>
       </c>
       <c r="B28" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3452,10 +3456,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571452</v>
+        <v>571283</v>
       </c>
       <c r="R28" t="n">
-        <v>6465730</v>
+        <v>6465682</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3492,7 +3496,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3501,7 +3505,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3520,37 +3523,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543509</v>
+        <v>129543603</v>
       </c>
       <c r="B29" t="n">
-        <v>92006</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3558,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571359</v>
+        <v>571376</v>
       </c>
       <c r="R29" t="n">
-        <v>6465750</v>
+        <v>6465679</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3598,7 +3614,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
+          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3607,7 +3623,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3626,54 +3641,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543344</v>
+        <v>129543537</v>
       </c>
       <c r="B30" t="n">
-        <v>57724</v>
+        <v>98727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3681,10 +3680,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571283</v>
+        <v>571452</v>
       </c>
       <c r="R30" t="n">
-        <v>6465682</v>
+        <v>6465730</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3721,7 +3720,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3730,6 +3729,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129543678</v>
+        <v>129543442</v>
       </c>
       <c r="B31" t="n">
         <v>98727</v>
@@ -3787,10 +3787,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571480</v>
+        <v>571390</v>
       </c>
       <c r="R31" t="n">
-        <v>6465780</v>
+        <v>6465781</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3855,7 +3855,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543442</v>
+        <v>129543678</v>
       </c>
       <c r="B32" t="n">
         <v>98727</v>
@@ -3894,10 +3894,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571390</v>
+        <v>571480</v>
       </c>
       <c r="R32" t="n">
-        <v>6465781</v>
+        <v>6465780</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4592,38 +4592,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543356</v>
+        <v>129543651</v>
       </c>
       <c r="B39" t="n">
-        <v>98727</v>
+        <v>79663</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4631,10 +4630,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571315</v>
+        <v>571336</v>
       </c>
       <c r="R39" t="n">
-        <v>6465727</v>
+        <v>6465638</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4667,11 +4666,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4806,7 +4800,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543624</v>
+        <v>129543356</v>
       </c>
       <c r="B41" t="n">
         <v>98727</v>
@@ -4845,10 +4839,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571370</v>
+        <v>571315</v>
       </c>
       <c r="R41" t="n">
-        <v>6465662</v>
+        <v>6465727</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4885,7 +4879,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ett tiotal</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4913,37 +4907,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543651</v>
+        <v>129543624</v>
       </c>
       <c r="B42" t="n">
-        <v>79663</v>
+        <v>98727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4951,10 +4946,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571336</v>
+        <v>571370</v>
       </c>
       <c r="R42" t="n">
-        <v>6465638</v>
+        <v>6465662</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4987,6 +4982,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -1314,38 +1314,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543430</v>
+        <v>129543463</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>79663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1353,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571367</v>
+        <v>571341</v>
       </c>
       <c r="R8" t="n">
-        <v>6465787</v>
+        <v>6465672</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,38 +1415,39 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543522</v>
+        <v>129543448</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>4773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1460,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571382</v>
+        <v>571395</v>
       </c>
       <c r="R9" t="n">
-        <v>6465758</v>
+        <v>6465767</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,11 +1491,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,37 +1518,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129543463</v>
+        <v>129543522</v>
       </c>
       <c r="B10" t="n">
-        <v>79663</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1566,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571341</v>
+        <v>571382</v>
       </c>
       <c r="R10" t="n">
-        <v>6465672</v>
+        <v>6465758</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,6 +1593,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,39 +1625,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543448</v>
+        <v>129543430</v>
       </c>
       <c r="B11" t="n">
-        <v>4773</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1669,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571395</v>
+        <v>571367</v>
       </c>
       <c r="R11" t="n">
-        <v>6465767</v>
+        <v>6465787</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,6 +1700,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2873,38 +2873,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129543484</v>
+        <v>129543457</v>
       </c>
       <c r="B23" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2912,10 +2911,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571327</v>
+        <v>571370</v>
       </c>
       <c r="R23" t="n">
-        <v>6465739</v>
+        <v>6465725</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,11 +2947,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2980,7 +2974,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129543348</v>
+        <v>129543484</v>
       </c>
       <c r="B24" t="n">
         <v>98727</v>
@@ -3019,10 +3013,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571288</v>
+        <v>571327</v>
       </c>
       <c r="R24" t="n">
-        <v>6465690</v>
+        <v>6465739</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3087,7 +3081,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543378</v>
+        <v>129543348</v>
       </c>
       <c r="B25" t="n">
         <v>98727</v>
@@ -3126,10 +3120,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571325</v>
+        <v>571288</v>
       </c>
       <c r="R25" t="n">
-        <v>6465727</v>
+        <v>6465690</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3194,37 +3188,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129543457</v>
+        <v>129543378</v>
       </c>
       <c r="B26" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3232,10 +3227,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571370</v>
+        <v>571325</v>
       </c>
       <c r="R26" t="n">
-        <v>6465725</v>
+        <v>6465727</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3268,6 +3263,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3523,50 +3523,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543603</v>
+        <v>129543537</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>98727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3574,10 +3562,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571376</v>
+        <v>571452</v>
       </c>
       <c r="R29" t="n">
-        <v>6465679</v>
+        <v>6465730</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,7 +3602,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3623,6 +3611,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3641,38 +3630,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543537</v>
+        <v>129543603</v>
       </c>
       <c r="B30" t="n">
-        <v>98727</v>
+        <v>57887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3680,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571452</v>
+        <v>571376</v>
       </c>
       <c r="R30" t="n">
-        <v>6465730</v>
+        <v>6465679</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3720,7 +3721,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3729,7 +3730,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3748,38 +3748,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129543442</v>
+        <v>129543655</v>
       </c>
       <c r="B31" t="n">
-        <v>98727</v>
+        <v>79663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3787,10 +3786,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571390</v>
+        <v>571375</v>
       </c>
       <c r="R31" t="n">
-        <v>6465781</v>
+        <v>6465649</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3823,11 +3822,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,7 +3849,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543678</v>
+        <v>129543442</v>
       </c>
       <c r="B32" t="n">
         <v>98727</v>
@@ -3894,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571480</v>
+        <v>571390</v>
       </c>
       <c r="R32" t="n">
-        <v>6465780</v>
+        <v>6465781</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3962,37 +3956,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543655</v>
+        <v>129543678</v>
       </c>
       <c r="B33" t="n">
-        <v>79663</v>
+        <v>98727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4000,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571375</v>
+        <v>571480</v>
       </c>
       <c r="R33" t="n">
-        <v>6465649</v>
+        <v>6465780</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4036,6 +4031,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4170,7 +4170,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543685</v>
+        <v>129543389</v>
       </c>
       <c r="B35" t="n">
         <v>98727</v>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>571461</v>
+        <v>571323</v>
       </c>
       <c r="R35" t="n">
-        <v>6465806</v>
+        <v>6465742</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4277,7 +4277,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129543389</v>
+        <v>129543685</v>
       </c>
       <c r="B36" t="n">
         <v>98727</v>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>571323</v>
+        <v>571461</v>
       </c>
       <c r="R36" t="n">
-        <v>6465742</v>
+        <v>6465806</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ett tjugotal</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4491,37 +4491,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129543564</v>
+        <v>129543356</v>
       </c>
       <c r="B38" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4529,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>571443</v>
+        <v>571315</v>
       </c>
       <c r="R38" t="n">
-        <v>6465681</v>
+        <v>6465727</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,6 +4566,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4592,37 +4598,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543651</v>
+        <v>129543361</v>
       </c>
       <c r="B39" t="n">
-        <v>79663</v>
+        <v>98727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4630,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571336</v>
+        <v>571328</v>
       </c>
       <c r="R39" t="n">
-        <v>6465638</v>
+        <v>6465727</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4666,6 +4673,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4693,7 +4705,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543361</v>
+        <v>129543624</v>
       </c>
       <c r="B40" t="n">
         <v>98727</v>
@@ -4732,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571328</v>
+        <v>571370</v>
       </c>
       <c r="R40" t="n">
-        <v>6465727</v>
+        <v>6465662</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4772,7 +4784,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4800,38 +4812,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543356</v>
+        <v>129543651</v>
       </c>
       <c r="B41" t="n">
-        <v>98727</v>
+        <v>79663</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4839,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571315</v>
+        <v>571336</v>
       </c>
       <c r="R41" t="n">
-        <v>6465727</v>
+        <v>6465638</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4875,11 +4886,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4907,38 +4913,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543624</v>
+        <v>129543564</v>
       </c>
       <c r="B42" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4946,10 +4951,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571370</v>
+        <v>571443</v>
       </c>
       <c r="R42" t="n">
-        <v>6465662</v>
+        <v>6465681</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4982,11 +4987,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -1314,37 +1314,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543463</v>
+        <v>129543522</v>
       </c>
       <c r="B8" t="n">
-        <v>79663</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1352,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571341</v>
+        <v>571382</v>
       </c>
       <c r="R8" t="n">
-        <v>6465672</v>
+        <v>6465758</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1389,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,39 +1421,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543448</v>
+        <v>129543430</v>
       </c>
       <c r="B9" t="n">
-        <v>4773</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1455,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571395</v>
+        <v>571367</v>
       </c>
       <c r="R9" t="n">
-        <v>6465767</v>
+        <v>6465787</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,6 +1496,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1518,38 +1528,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129543522</v>
+        <v>129543463</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>79663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1557,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571382</v>
+        <v>571341</v>
       </c>
       <c r="R10" t="n">
-        <v>6465758</v>
+        <v>6465672</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1625,38 +1629,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543430</v>
+        <v>129543448</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>4773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1664,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571367</v>
+        <v>571395</v>
       </c>
       <c r="R11" t="n">
-        <v>6465787</v>
+        <v>6465767</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,11 +1705,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2350,37 +2350,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543452</v>
+        <v>129543383</v>
       </c>
       <c r="B18" t="n">
-        <v>92195</v>
+        <v>105793</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5454</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2388,10 +2389,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571381</v>
+        <v>571325</v>
       </c>
       <c r="R18" t="n">
-        <v>6465712</v>
+        <v>6465727</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,6 +2425,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2451,38 +2457,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129543392</v>
+        <v>129543452</v>
       </c>
       <c r="B19" t="n">
-        <v>98727</v>
+        <v>92195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5454</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2490,10 +2495,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571309</v>
+        <v>571381</v>
       </c>
       <c r="R19" t="n">
-        <v>6465740</v>
+        <v>6465712</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,11 +2531,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2558,32 +2558,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129543383</v>
+        <v>129543392</v>
       </c>
       <c r="B20" t="n">
-        <v>105793</v>
+        <v>98727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571325</v>
+        <v>571309</v>
       </c>
       <c r="R20" t="n">
-        <v>6465727</v>
+        <v>6465740</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ett tjugotal</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3295,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543509</v>
+        <v>129543537</v>
       </c>
       <c r="B27" t="n">
-        <v>92006</v>
+        <v>98727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3306,26 +3306,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3333,10 +3334,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571359</v>
+        <v>571452</v>
       </c>
       <c r="R27" t="n">
-        <v>6465750</v>
+        <v>6465730</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3373,7 +3374,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3401,54 +3402,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543344</v>
+        <v>129543509</v>
       </c>
       <c r="B28" t="n">
-        <v>57724</v>
+        <v>92006</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3456,10 +3440,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571283</v>
+        <v>571359</v>
       </c>
       <c r="R28" t="n">
-        <v>6465682</v>
+        <v>6465750</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3496,7 +3480,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
+          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3505,6 +3489,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3523,38 +3508,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543537</v>
+        <v>129543344</v>
       </c>
       <c r="B29" t="n">
-        <v>98727</v>
+        <v>57724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3562,10 +3563,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571452</v>
+        <v>571283</v>
       </c>
       <c r="R29" t="n">
-        <v>6465730</v>
+        <v>6465682</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,7 +3603,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3611,7 +3612,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3849,7 +3849,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543442</v>
+        <v>129543678</v>
       </c>
       <c r="B32" t="n">
         <v>98727</v>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571390</v>
+        <v>571480</v>
       </c>
       <c r="R32" t="n">
-        <v>6465781</v>
+        <v>6465780</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3956,7 +3956,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543678</v>
+        <v>129543442</v>
       </c>
       <c r="B33" t="n">
         <v>98727</v>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571480</v>
+        <v>571390</v>
       </c>
       <c r="R33" t="n">
-        <v>6465780</v>
+        <v>6465781</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4491,38 +4491,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129543356</v>
+        <v>129543564</v>
       </c>
       <c r="B38" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4530,10 +4529,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>571315</v>
+        <v>571443</v>
       </c>
       <c r="R38" t="n">
-        <v>6465727</v>
+        <v>6465681</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,11 +4565,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4598,38 +4592,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543361</v>
+        <v>129543651</v>
       </c>
       <c r="B39" t="n">
-        <v>98727</v>
+        <v>79663</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4637,10 +4630,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571328</v>
+        <v>571336</v>
       </c>
       <c r="R39" t="n">
-        <v>6465727</v>
+        <v>6465638</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4673,11 +4666,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4705,7 +4693,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543624</v>
+        <v>129543356</v>
       </c>
       <c r="B40" t="n">
         <v>98727</v>
@@ -4744,10 +4732,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571370</v>
+        <v>571315</v>
       </c>
       <c r="R40" t="n">
-        <v>6465662</v>
+        <v>6465727</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4784,7 +4772,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ett tiotal</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4812,37 +4800,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543651</v>
+        <v>129543361</v>
       </c>
       <c r="B41" t="n">
-        <v>79663</v>
+        <v>98727</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4850,10 +4839,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571336</v>
+        <v>571328</v>
       </c>
       <c r="R41" t="n">
-        <v>6465638</v>
+        <v>6465727</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,6 +4875,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4913,37 +4907,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543564</v>
+        <v>129543624</v>
       </c>
       <c r="B42" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4951,10 +4946,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571443</v>
+        <v>571370</v>
       </c>
       <c r="R42" t="n">
-        <v>6465681</v>
+        <v>6465662</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4987,6 +4982,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5014,37 +5014,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129543662</v>
+        <v>129543395</v>
       </c>
       <c r="B43" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5052,10 +5053,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>571429</v>
+        <v>571344</v>
       </c>
       <c r="R43" t="n">
-        <v>6465708</v>
+        <v>6465783</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5088,6 +5089,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5115,38 +5121,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129543395</v>
+        <v>129543662</v>
       </c>
       <c r="B44" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5154,10 +5159,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571344</v>
+        <v>571429</v>
       </c>
       <c r="R44" t="n">
-        <v>6465783</v>
+        <v>6465708</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5190,11 +5195,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -1100,7 +1100,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543327</v>
+        <v>129543544</v>
       </c>
       <c r="B6" t="n">
         <v>98727</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571291</v>
+        <v>571456</v>
       </c>
       <c r="R6" t="n">
-        <v>6465665</v>
+        <v>6465730</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543544</v>
+        <v>129543327</v>
       </c>
       <c r="B7" t="n">
         <v>98727</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571456</v>
+        <v>571291</v>
       </c>
       <c r="R7" t="n">
-        <v>6465730</v>
+        <v>6465665</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,38 +1314,39 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543522</v>
+        <v>129543448</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>4773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1353,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571382</v>
+        <v>571395</v>
       </c>
       <c r="R8" t="n">
-        <v>6465758</v>
+        <v>6465767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,11 +1390,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1528,37 +1524,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129543463</v>
+        <v>129543522</v>
       </c>
       <c r="B10" t="n">
-        <v>79663</v>
+        <v>98727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1566,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571341</v>
+        <v>571382</v>
       </c>
       <c r="R10" t="n">
-        <v>6465672</v>
+        <v>6465758</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,6 +1599,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,39 +1631,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543448</v>
+        <v>129543463</v>
       </c>
       <c r="B11" t="n">
-        <v>4773</v>
+        <v>79663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100299</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571395</v>
+        <v>571341</v>
       </c>
       <c r="R11" t="n">
-        <v>6465767</v>
+        <v>6465672</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2457,37 +2457,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129543452</v>
+        <v>129543392</v>
       </c>
       <c r="B19" t="n">
-        <v>92195</v>
+        <v>98727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5454</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2495,10 +2496,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571381</v>
+        <v>571309</v>
       </c>
       <c r="R19" t="n">
-        <v>6465712</v>
+        <v>6465740</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,6 +2532,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2558,38 +2564,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129543392</v>
+        <v>129543452</v>
       </c>
       <c r="B20" t="n">
-        <v>98727</v>
+        <v>92195</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5454</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2597,10 +2602,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571309</v>
+        <v>571381</v>
       </c>
       <c r="R20" t="n">
-        <v>6465740</v>
+        <v>6465712</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,11 +2638,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2974,7 +2974,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129543484</v>
+        <v>129543378</v>
       </c>
       <c r="B24" t="n">
         <v>98727</v>
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571327</v>
+        <v>571325</v>
       </c>
       <c r="R24" t="n">
-        <v>6465739</v>
+        <v>6465727</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,7 +3081,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543348</v>
+        <v>129543484</v>
       </c>
       <c r="B25" t="n">
         <v>98727</v>
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571288</v>
+        <v>571327</v>
       </c>
       <c r="R25" t="n">
-        <v>6465690</v>
+        <v>6465739</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129543378</v>
+        <v>129543348</v>
       </c>
       <c r="B26" t="n">
         <v>98727</v>
@@ -3227,10 +3227,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571325</v>
+        <v>571288</v>
       </c>
       <c r="R26" t="n">
-        <v>6465727</v>
+        <v>6465690</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3508,10 +3508,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543344</v>
+        <v>129543603</v>
       </c>
       <c r="B29" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3519,26 +3519,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3546,11 +3546,7 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -3563,10 +3559,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571283</v>
+        <v>571376</v>
       </c>
       <c r="R29" t="n">
-        <v>6465682</v>
+        <v>6465679</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3603,7 +3599,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
+          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3630,10 +3626,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543603</v>
+        <v>129543344</v>
       </c>
       <c r="B30" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3641,26 +3637,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3668,7 +3664,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571376</v>
+        <v>571283</v>
       </c>
       <c r="R30" t="n">
-        <v>6465679</v>
+        <v>6465682</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
+          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4170,7 +4170,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543389</v>
+        <v>129543685</v>
       </c>
       <c r="B35" t="n">
         <v>98727</v>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>571323</v>
+        <v>571461</v>
       </c>
       <c r="R35" t="n">
-        <v>6465742</v>
+        <v>6465806</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ett tjugotal</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4277,7 +4277,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129543685</v>
+        <v>129543389</v>
       </c>
       <c r="B36" t="n">
         <v>98727</v>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>571461</v>
+        <v>571323</v>
       </c>
       <c r="R36" t="n">
-        <v>6465806</v>
+        <v>6465742</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4693,7 +4693,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543356</v>
+        <v>129543361</v>
       </c>
       <c r="B40" t="n">
         <v>98727</v>
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571315</v>
+        <v>571328</v>
       </c>
       <c r="R40" t="n">
         <v>6465727</v>
@@ -4800,7 +4800,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543361</v>
+        <v>129543624</v>
       </c>
       <c r="B41" t="n">
         <v>98727</v>
@@ -4839,10 +4839,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571328</v>
+        <v>571370</v>
       </c>
       <c r="R41" t="n">
-        <v>6465727</v>
+        <v>6465662</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4907,7 +4907,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543624</v>
+        <v>129543356</v>
       </c>
       <c r="B42" t="n">
         <v>98727</v>
@@ -4946,10 +4946,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571370</v>
+        <v>571315</v>
       </c>
       <c r="R42" t="n">
-        <v>6465662</v>
+        <v>6465727</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ett tiotal</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5014,38 +5014,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129543395</v>
+        <v>129543662</v>
       </c>
       <c r="B43" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5053,10 +5052,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>571344</v>
+        <v>571429</v>
       </c>
       <c r="R43" t="n">
-        <v>6465783</v>
+        <v>6465708</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5089,11 +5088,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5121,37 +5115,38 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129543662</v>
+        <v>129543395</v>
       </c>
       <c r="B44" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5159,10 +5154,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>571429</v>
+        <v>571344</v>
       </c>
       <c r="R44" t="n">
-        <v>6465708</v>
+        <v>6465783</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5195,6 +5190,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -1100,7 +1100,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543544</v>
+        <v>129543327</v>
       </c>
       <c r="B6" t="n">
         <v>98727</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571456</v>
+        <v>571291</v>
       </c>
       <c r="R6" t="n">
-        <v>6465730</v>
+        <v>6465665</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543327</v>
+        <v>129543544</v>
       </c>
       <c r="B7" t="n">
         <v>98727</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571291</v>
+        <v>571456</v>
       </c>
       <c r="R7" t="n">
-        <v>6465665</v>
+        <v>6465730</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,39 +1314,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543448</v>
+        <v>129543463</v>
       </c>
       <c r="B8" t="n">
-        <v>4773</v>
+        <v>79663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1354,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571395</v>
+        <v>571341</v>
       </c>
       <c r="R8" t="n">
-        <v>6465767</v>
+        <v>6465672</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,38 +1415,39 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543430</v>
+        <v>129543448</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>4773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1456,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571367</v>
+        <v>571395</v>
       </c>
       <c r="R9" t="n">
-        <v>6465787</v>
+        <v>6465767</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,11 +1491,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,37 +1625,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543463</v>
+        <v>129543430</v>
       </c>
       <c r="B11" t="n">
-        <v>79663</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1669,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571341</v>
+        <v>571367</v>
       </c>
       <c r="R11" t="n">
-        <v>6465672</v>
+        <v>6465787</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,6 +1700,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2350,38 +2350,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543383</v>
+        <v>129543452</v>
       </c>
       <c r="B18" t="n">
-        <v>105793</v>
+        <v>92195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>5454</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2389,10 +2388,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571325</v>
+        <v>571381</v>
       </c>
       <c r="R18" t="n">
-        <v>6465727</v>
+        <v>6465712</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2425,11 +2424,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2457,32 +2451,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129543392</v>
+        <v>129543383</v>
       </c>
       <c r="B19" t="n">
-        <v>98727</v>
+        <v>105793</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2496,10 +2490,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571309</v>
+        <v>571325</v>
       </c>
       <c r="R19" t="n">
-        <v>6465740</v>
+        <v>6465727</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2536,7 +2530,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2564,37 +2558,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129543452</v>
+        <v>129543392</v>
       </c>
       <c r="B20" t="n">
-        <v>92195</v>
+        <v>98727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5454</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2602,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571381</v>
+        <v>571309</v>
       </c>
       <c r="R20" t="n">
-        <v>6465712</v>
+        <v>6465740</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,6 +2633,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2873,37 +2873,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129543457</v>
+        <v>129543484</v>
       </c>
       <c r="B23" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2911,10 +2912,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571370</v>
+        <v>571327</v>
       </c>
       <c r="R23" t="n">
-        <v>6465725</v>
+        <v>6465739</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2947,6 +2948,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2974,7 +2980,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129543378</v>
+        <v>129543348</v>
       </c>
       <c r="B24" t="n">
         <v>98727</v>
@@ -3013,10 +3019,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571325</v>
+        <v>571288</v>
       </c>
       <c r="R24" t="n">
-        <v>6465727</v>
+        <v>6465690</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,7 +3087,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543484</v>
+        <v>129543378</v>
       </c>
       <c r="B25" t="n">
         <v>98727</v>
@@ -3120,10 +3126,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571327</v>
+        <v>571325</v>
       </c>
       <c r="R25" t="n">
-        <v>6465739</v>
+        <v>6465727</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3188,38 +3194,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129543348</v>
+        <v>129543457</v>
       </c>
       <c r="B26" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3227,10 +3232,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571288</v>
+        <v>571370</v>
       </c>
       <c r="R26" t="n">
-        <v>6465690</v>
+        <v>6465725</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3263,11 +3268,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3295,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543537</v>
+        <v>129543509</v>
       </c>
       <c r="B27" t="n">
-        <v>98727</v>
+        <v>92006</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3306,27 +3306,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3334,10 +3333,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571452</v>
+        <v>571359</v>
       </c>
       <c r="R27" t="n">
-        <v>6465730</v>
+        <v>6465750</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3374,7 +3373,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3402,10 +3401,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543509</v>
+        <v>129543537</v>
       </c>
       <c r="B28" t="n">
-        <v>92006</v>
+        <v>98727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3413,26 +3412,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571359</v>
+        <v>571452</v>
       </c>
       <c r="R28" t="n">
-        <v>6465750</v>
+        <v>6465730</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3508,10 +3508,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543603</v>
+        <v>129543344</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3519,26 +3519,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3546,7 +3546,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -3559,10 +3563,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571376</v>
+        <v>571283</v>
       </c>
       <c r="R29" t="n">
-        <v>6465679</v>
+        <v>6465682</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3599,7 +3603,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
+          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3626,10 +3630,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543344</v>
+        <v>129543603</v>
       </c>
       <c r="B30" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3637,26 +3641,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3664,11 +3668,7 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571283</v>
+        <v>571376</v>
       </c>
       <c r="R30" t="n">
-        <v>6465682</v>
+        <v>6465679</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3721,7 +3721,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
+          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4170,7 +4170,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543685</v>
+        <v>129543389</v>
       </c>
       <c r="B35" t="n">
         <v>98727</v>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>571461</v>
+        <v>571323</v>
       </c>
       <c r="R35" t="n">
-        <v>6465806</v>
+        <v>6465742</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4277,7 +4277,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129543389</v>
+        <v>129543685</v>
       </c>
       <c r="B36" t="n">
         <v>98727</v>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>571323</v>
+        <v>571461</v>
       </c>
       <c r="R36" t="n">
-        <v>6465742</v>
+        <v>6465806</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ett tjugotal</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4491,37 +4491,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129543564</v>
+        <v>129543356</v>
       </c>
       <c r="B38" t="n">
-        <v>91553</v>
+        <v>98727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4529,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>571443</v>
+        <v>571315</v>
       </c>
       <c r="R38" t="n">
-        <v>6465681</v>
+        <v>6465727</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,6 +4566,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4592,37 +4598,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543651</v>
+        <v>129543361</v>
       </c>
       <c r="B39" t="n">
-        <v>79663</v>
+        <v>98727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4630,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571336</v>
+        <v>571328</v>
       </c>
       <c r="R39" t="n">
-        <v>6465638</v>
+        <v>6465727</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4666,6 +4673,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4693,7 +4705,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543361</v>
+        <v>129543624</v>
       </c>
       <c r="B40" t="n">
         <v>98727</v>
@@ -4732,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571328</v>
+        <v>571370</v>
       </c>
       <c r="R40" t="n">
-        <v>6465727</v>
+        <v>6465662</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4772,7 +4784,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4800,38 +4812,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543624</v>
+        <v>129543564</v>
       </c>
       <c r="B41" t="n">
-        <v>98727</v>
+        <v>91553</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4839,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571370</v>
+        <v>571443</v>
       </c>
       <c r="R41" t="n">
-        <v>6465662</v>
+        <v>6465681</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4875,11 +4886,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4907,38 +4913,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543356</v>
+        <v>129543651</v>
       </c>
       <c r="B42" t="n">
-        <v>98727</v>
+        <v>79663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4946,10 +4951,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571315</v>
+        <v>571336</v>
       </c>
       <c r="R42" t="n">
-        <v>6465727</v>
+        <v>6465638</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4982,11 +4987,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>129543469</v>
       </c>
       <c r="B5" t="n">
-        <v>96169</v>
+        <v>96198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>129543327</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>129543544</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>129543463</v>
       </c>
       <c r="B8" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,39 +1415,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543448</v>
+        <v>129543522</v>
       </c>
       <c r="B9" t="n">
-        <v>4773</v>
+        <v>98756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1455,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571395</v>
+        <v>571382</v>
       </c>
       <c r="R9" t="n">
-        <v>6465767</v>
+        <v>6465758</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1518,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129543522</v>
+        <v>129543430</v>
       </c>
       <c r="B10" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571382</v>
+        <v>571367</v>
       </c>
       <c r="R10" t="n">
-        <v>6465758</v>
+        <v>6465787</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,38 +1629,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543430</v>
+        <v>129543448</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>4773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1664,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571367</v>
+        <v>571395</v>
       </c>
       <c r="R11" t="n">
-        <v>6465787</v>
+        <v>6465767</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,11 +1705,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1735,7 @@
         <v>129543553</v>
       </c>
       <c r="B12" t="n">
-        <v>91567</v>
+        <v>91595</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>129543434</v>
       </c>
       <c r="B13" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>129543516</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>129543475</v>
       </c>
       <c r="B15" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>129543571</v>
       </c>
       <c r="B16" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2249,37 +2249,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543676</v>
+        <v>129543383</v>
       </c>
       <c r="B17" t="n">
-        <v>91553</v>
+        <v>105822</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2287,10 +2288,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571480</v>
+        <v>571325</v>
       </c>
       <c r="R17" t="n">
-        <v>6465733</v>
+        <v>6465727</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2323,6 +2324,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2350,37 +2356,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543452</v>
+        <v>129543392</v>
       </c>
       <c r="B18" t="n">
-        <v>92195</v>
+        <v>98756</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5454</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2388,10 +2395,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571381</v>
+        <v>571309</v>
       </c>
       <c r="R18" t="n">
-        <v>6465712</v>
+        <v>6465740</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,6 +2431,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2451,38 +2463,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129543383</v>
+        <v>129543676</v>
       </c>
       <c r="B19" t="n">
-        <v>105793</v>
+        <v>91581</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2490,10 +2501,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571325</v>
+        <v>571480</v>
       </c>
       <c r="R19" t="n">
-        <v>6465727</v>
+        <v>6465733</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,11 +2537,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2558,38 +2564,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129543392</v>
+        <v>129543452</v>
       </c>
       <c r="B20" t="n">
-        <v>98727</v>
+        <v>92223</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>5454</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2597,10 +2602,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571309</v>
+        <v>571381</v>
       </c>
       <c r="R20" t="n">
-        <v>6465740</v>
+        <v>6465712</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,11 +2638,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2668,7 +2668,7 @@
         <v>129543658</v>
       </c>
       <c r="B21" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129543526</v>
       </c>
       <c r="B22" t="n">
-        <v>105793</v>
+        <v>105822</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2873,38 +2873,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129543484</v>
+        <v>129543457</v>
       </c>
       <c r="B23" t="n">
-        <v>98727</v>
+        <v>91581</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2912,10 +2911,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571327</v>
+        <v>571370</v>
       </c>
       <c r="R23" t="n">
-        <v>6465739</v>
+        <v>6465725</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,11 +2947,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2980,10 +2974,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129543348</v>
+        <v>129543484</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3019,10 +3013,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571288</v>
+        <v>571327</v>
       </c>
       <c r="R24" t="n">
-        <v>6465690</v>
+        <v>6465739</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3087,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543378</v>
+        <v>129543348</v>
       </c>
       <c r="B25" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3126,10 +3120,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571325</v>
+        <v>571288</v>
       </c>
       <c r="R25" t="n">
-        <v>6465727</v>
+        <v>6465690</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3194,37 +3188,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129543457</v>
+        <v>129543378</v>
       </c>
       <c r="B26" t="n">
-        <v>91553</v>
+        <v>98756</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3232,10 +3227,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571370</v>
+        <v>571325</v>
       </c>
       <c r="R26" t="n">
-        <v>6465725</v>
+        <v>6465727</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3268,6 +3263,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3298,7 +3298,7 @@
         <v>129543509</v>
       </c>
       <c r="B27" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,38 +3401,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543537</v>
+        <v>129543344</v>
       </c>
       <c r="B28" t="n">
-        <v>98727</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3440,10 +3456,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571452</v>
+        <v>571283</v>
       </c>
       <c r="R28" t="n">
-        <v>6465730</v>
+        <v>6465682</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3480,7 +3496,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3489,7 +3505,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3508,10 +3523,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543344</v>
+        <v>129543603</v>
       </c>
       <c r="B29" t="n">
-        <v>57724</v>
+        <v>57890</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3519,26 +3534,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3546,11 +3561,7 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -3563,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571283</v>
+        <v>571376</v>
       </c>
       <c r="R29" t="n">
-        <v>6465682</v>
+        <v>6465679</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3603,7 +3614,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
+          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3630,50 +3641,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543603</v>
+        <v>129543537</v>
       </c>
       <c r="B30" t="n">
-        <v>57887</v>
+        <v>98756</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3681,10 +3680,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571376</v>
+        <v>571452</v>
       </c>
       <c r="R30" t="n">
-        <v>6465679</v>
+        <v>6465730</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3721,7 +3720,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3730,6 +3729,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>129543655</v>
       </c>
       <c r="B31" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>129543678</v>
       </c>
       <c r="B32" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>129543442</v>
       </c>
       <c r="B33" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>129543686</v>
       </c>
       <c r="B34" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>129543389</v>
       </c>
       <c r="B35" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>129543685</v>
       </c>
       <c r="B36" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>129543368</v>
       </c>
       <c r="B37" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4491,38 +4491,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129543356</v>
+        <v>129543564</v>
       </c>
       <c r="B38" t="n">
-        <v>98727</v>
+        <v>91581</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4530,10 +4529,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>571315</v>
+        <v>571443</v>
       </c>
       <c r="R38" t="n">
-        <v>6465727</v>
+        <v>6465681</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,11 +4565,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4598,38 +4592,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543361</v>
+        <v>129543651</v>
       </c>
       <c r="B39" t="n">
-        <v>98727</v>
+        <v>79689</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4637,10 +4630,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571328</v>
+        <v>571336</v>
       </c>
       <c r="R39" t="n">
-        <v>6465727</v>
+        <v>6465638</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4673,11 +4666,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4705,10 +4693,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543624</v>
+        <v>129543356</v>
       </c>
       <c r="B40" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4744,10 +4732,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571370</v>
+        <v>571315</v>
       </c>
       <c r="R40" t="n">
-        <v>6465662</v>
+        <v>6465727</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4784,7 +4772,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ett tiotal</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4812,37 +4800,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543564</v>
+        <v>129543361</v>
       </c>
       <c r="B41" t="n">
-        <v>91553</v>
+        <v>98756</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4850,10 +4839,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571443</v>
+        <v>571328</v>
       </c>
       <c r="R41" t="n">
-        <v>6465681</v>
+        <v>6465727</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,6 +4875,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4913,37 +4907,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543651</v>
+        <v>129543624</v>
       </c>
       <c r="B42" t="n">
-        <v>79663</v>
+        <v>98756</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4951,10 +4946,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571336</v>
+        <v>571370</v>
       </c>
       <c r="R42" t="n">
-        <v>6465638</v>
+        <v>6465662</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4987,6 +4982,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5017,7 +5017,7 @@
         <v>129543662</v>
       </c>
       <c r="B43" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>129543395</v>
       </c>
       <c r="B44" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -3295,37 +3295,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543509</v>
+        <v>129543603</v>
       </c>
       <c r="B27" t="n">
-        <v>92034</v>
+        <v>57890</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3333,10 +3346,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571359</v>
+        <v>571376</v>
       </c>
       <c r="R27" t="n">
-        <v>6465750</v>
+        <v>6465679</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3373,7 +3386,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
+          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3382,7 +3395,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3401,54 +3413,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543344</v>
+        <v>129543537</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>98756</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3456,10 +3452,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571283</v>
+        <v>571452</v>
       </c>
       <c r="R28" t="n">
-        <v>6465682</v>
+        <v>6465730</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3496,7 +3492,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3505,6 +3501,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3523,10 +3520,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543603</v>
+        <v>129543344</v>
       </c>
       <c r="B29" t="n">
-        <v>57890</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3534,26 +3531,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3561,7 +3558,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -3574,10 +3575,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571376</v>
+        <v>571283</v>
       </c>
       <c r="R29" t="n">
-        <v>6465679</v>
+        <v>6465682</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,7 +3615,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
+          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3641,10 +3642,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543537</v>
+        <v>129543509</v>
       </c>
       <c r="B30" t="n">
-        <v>98756</v>
+        <v>92034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3652,27 +3653,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571452</v>
+        <v>571359</v>
       </c>
       <c r="R30" t="n">
-        <v>6465730</v>
+        <v>6465750</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4491,10 +4491,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129543564</v>
+        <v>129543651</v>
       </c>
       <c r="B38" t="n">
-        <v>91581</v>
+        <v>79689</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4502,21 +4502,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>571443</v>
+        <v>571336</v>
       </c>
       <c r="R38" t="n">
-        <v>6465681</v>
+        <v>6465638</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4592,37 +4592,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543651</v>
+        <v>129543356</v>
       </c>
       <c r="B39" t="n">
-        <v>79689</v>
+        <v>98756</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4630,10 +4631,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571336</v>
+        <v>571315</v>
       </c>
       <c r="R39" t="n">
-        <v>6465638</v>
+        <v>6465727</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4666,6 +4667,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4693,7 +4699,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543356</v>
+        <v>129543361</v>
       </c>
       <c r="B40" t="n">
         <v>98756</v>
@@ -4732,7 +4738,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571315</v>
+        <v>571328</v>
       </c>
       <c r="R40" t="n">
         <v>6465727</v>
@@ -4800,7 +4806,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543361</v>
+        <v>129543624</v>
       </c>
       <c r="B41" t="n">
         <v>98756</v>
@@ -4839,10 +4845,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571328</v>
+        <v>571370</v>
       </c>
       <c r="R41" t="n">
-        <v>6465727</v>
+        <v>6465662</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4879,7 +4885,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4907,38 +4913,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543624</v>
+        <v>129543564</v>
       </c>
       <c r="B42" t="n">
-        <v>98756</v>
+        <v>91581</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4946,10 +4951,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571370</v>
+        <v>571443</v>
       </c>
       <c r="R42" t="n">
-        <v>6465662</v>
+        <v>6465681</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4982,11 +4987,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,7 +1001,7 @@
         <v>129543469</v>
       </c>
       <c r="B5" t="n">
-        <v>96198</v>
+        <v>96210</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543327</v>
+        <v>129543544</v>
       </c>
       <c r="B6" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571291</v>
+        <v>571456</v>
       </c>
       <c r="R6" t="n">
-        <v>6465665</v>
+        <v>6465730</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543544</v>
+        <v>129543327</v>
       </c>
       <c r="B7" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571456</v>
+        <v>571291</v>
       </c>
       <c r="R7" t="n">
-        <v>6465730</v>
+        <v>6465665</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
         <v>129543463</v>
       </c>
       <c r="B8" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>129543522</v>
       </c>
       <c r="B9" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>129543430</v>
       </c>
       <c r="B10" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>129543553</v>
       </c>
       <c r="B12" t="n">
-        <v>91595</v>
+        <v>91601</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>129543434</v>
       </c>
       <c r="B13" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>129543516</v>
       </c>
       <c r="B14" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>129543475</v>
       </c>
       <c r="B15" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>129543571</v>
       </c>
       <c r="B16" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2249,38 +2249,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543383</v>
+        <v>129543676</v>
       </c>
       <c r="B17" t="n">
-        <v>105822</v>
+        <v>91587</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2288,10 +2287,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571325</v>
+        <v>571480</v>
       </c>
       <c r="R17" t="n">
-        <v>6465727</v>
+        <v>6465733</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2324,11 +2323,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2356,38 +2350,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543392</v>
+        <v>129543452</v>
       </c>
       <c r="B18" t="n">
-        <v>98756</v>
+        <v>92229</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5454</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2395,10 +2388,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571309</v>
+        <v>571381</v>
       </c>
       <c r="R18" t="n">
-        <v>6465740</v>
+        <v>6465712</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2431,11 +2424,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2463,37 +2451,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129543676</v>
+        <v>129543392</v>
       </c>
       <c r="B19" t="n">
-        <v>91581</v>
+        <v>98768</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2501,10 +2490,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571480</v>
+        <v>571309</v>
       </c>
       <c r="R19" t="n">
-        <v>6465733</v>
+        <v>6465740</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2537,6 +2526,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2564,37 +2558,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129543452</v>
+        <v>129543383</v>
       </c>
       <c r="B20" t="n">
-        <v>92223</v>
+        <v>105834</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5454</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2602,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571381</v>
+        <v>571325</v>
       </c>
       <c r="R20" t="n">
-        <v>6465712</v>
+        <v>6465727</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,6 +2633,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2668,7 +2668,7 @@
         <v>129543658</v>
       </c>
       <c r="B21" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129543526</v>
       </c>
       <c r="B22" t="n">
-        <v>105822</v>
+        <v>105834</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>129543457</v>
       </c>
       <c r="B23" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2974,10 +2974,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129543484</v>
+        <v>129543348</v>
       </c>
       <c r="B24" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571327</v>
+        <v>571288</v>
       </c>
       <c r="R24" t="n">
-        <v>6465739</v>
+        <v>6465690</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543348</v>
+        <v>129543484</v>
       </c>
       <c r="B25" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571288</v>
+        <v>571327</v>
       </c>
       <c r="R25" t="n">
-        <v>6465690</v>
+        <v>6465739</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3191,7 +3191,7 @@
         <v>129543378</v>
       </c>
       <c r="B26" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3295,50 +3295,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543603</v>
+        <v>129543509</v>
       </c>
       <c r="B27" t="n">
-        <v>57890</v>
+        <v>92040</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3346,10 +3333,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571376</v>
+        <v>571359</v>
       </c>
       <c r="R27" t="n">
-        <v>6465679</v>
+        <v>6465750</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3386,7 +3373,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
+          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3395,6 +3382,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3413,38 +3401,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543537</v>
+        <v>129543344</v>
       </c>
       <c r="B28" t="n">
-        <v>98756</v>
+        <v>57732</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3452,10 +3456,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571452</v>
+        <v>571283</v>
       </c>
       <c r="R28" t="n">
-        <v>6465730</v>
+        <v>6465682</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3492,7 +3496,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3501,7 +3505,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3520,54 +3523,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543344</v>
+        <v>129543537</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>98768</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3575,10 +3562,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571283</v>
+        <v>571452</v>
       </c>
       <c r="R29" t="n">
-        <v>6465682</v>
+        <v>6465730</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3615,7 +3602,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3624,6 +3611,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3642,37 +3630,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543509</v>
+        <v>129543603</v>
       </c>
       <c r="B30" t="n">
-        <v>92034</v>
+        <v>57895</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3680,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571359</v>
+        <v>571376</v>
       </c>
       <c r="R30" t="n">
-        <v>6465750</v>
+        <v>6465679</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3720,7 +3721,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
+          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3729,7 +3730,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3751,7 +3751,7 @@
         <v>129543655</v>
       </c>
       <c r="B31" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>129543678</v>
       </c>
       <c r="B32" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>129543442</v>
       </c>
       <c r="B33" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>129543686</v>
       </c>
       <c r="B34" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>129543389</v>
       </c>
       <c r="B35" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>129543685</v>
       </c>
       <c r="B36" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>129543368</v>
       </c>
       <c r="B37" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>129543651</v>
       </c>
       <c r="B38" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>129543356</v>
       </c>
       <c r="B39" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4699,10 +4699,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543361</v>
+        <v>129543624</v>
       </c>
       <c r="B40" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4738,10 +4738,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571328</v>
+        <v>571370</v>
       </c>
       <c r="R40" t="n">
-        <v>6465727</v>
+        <v>6465662</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4806,10 +4806,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543624</v>
+        <v>129543361</v>
       </c>
       <c r="B41" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571370</v>
+        <v>571328</v>
       </c>
       <c r="R41" t="n">
-        <v>6465662</v>
+        <v>6465727</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ett tiotal</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4916,7 +4916,7 @@
         <v>129543564</v>
       </c>
       <c r="B42" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>129543662</v>
       </c>
       <c r="B43" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>129543395</v>
       </c>
       <c r="B44" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5220,6 +5220,246 @@
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129741149</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>571313</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6465722</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Revirparet i sin hemvist naturskogen.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129741141</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Glupen- nedklassad naturvårdsskog, Ög</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>571422</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6465772</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Östra Ryd</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Den extrema mängden med död ved i naturskogen är ett smörgåsbord för spillkråkan. Resterande hygges- och plantagelandskapet i anslutning bjuder inte så mycket.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>129543469</v>
       </c>
       <c r="B5" t="n">
-        <v>96210</v>
+        <v>96211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543544</v>
+        <v>129543327</v>
       </c>
       <c r="B6" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571456</v>
+        <v>571291</v>
       </c>
       <c r="R6" t="n">
-        <v>6465730</v>
+        <v>6465665</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543327</v>
+        <v>129543544</v>
       </c>
       <c r="B7" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571291</v>
+        <v>571456</v>
       </c>
       <c r="R7" t="n">
-        <v>6465665</v>
+        <v>6465730</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
         <v>129543463</v>
       </c>
       <c r="B8" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>129543522</v>
       </c>
       <c r="B9" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>129543430</v>
       </c>
       <c r="B10" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>129543553</v>
       </c>
       <c r="B12" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>129543434</v>
       </c>
       <c r="B13" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>129543516</v>
       </c>
       <c r="B14" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>129543475</v>
       </c>
       <c r="B15" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>129543571</v>
       </c>
       <c r="B16" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2249,10 +2249,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543676</v>
+        <v>129543452</v>
       </c>
       <c r="B17" t="n">
-        <v>91587</v>
+        <v>92230</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2260,21 +2260,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5454</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571480</v>
+        <v>571381</v>
       </c>
       <c r="R17" t="n">
-        <v>6465733</v>
+        <v>6465712</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543452</v>
+        <v>129543676</v>
       </c>
       <c r="B18" t="n">
-        <v>92229</v>
+        <v>91588</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,21 +2361,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5454</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571381</v>
+        <v>571480</v>
       </c>
       <c r="R18" t="n">
-        <v>6465712</v>
+        <v>6465733</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,7 +2454,7 @@
         <v>129543392</v>
       </c>
       <c r="B19" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>129543383</v>
       </c>
       <c r="B20" t="n">
-        <v>105834</v>
+        <v>105835</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>129543658</v>
       </c>
       <c r="B21" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129543526</v>
       </c>
       <c r="B22" t="n">
-        <v>105834</v>
+        <v>105835</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2873,37 +2873,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129543457</v>
+        <v>129543484</v>
       </c>
       <c r="B23" t="n">
-        <v>91587</v>
+        <v>98769</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2911,10 +2912,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571370</v>
+        <v>571327</v>
       </c>
       <c r="R23" t="n">
-        <v>6465725</v>
+        <v>6465739</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2947,6 +2948,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2977,7 +2983,7 @@
         <v>129543348</v>
       </c>
       <c r="B24" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3081,10 +3087,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543484</v>
+        <v>129543378</v>
       </c>
       <c r="B25" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3120,10 +3126,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571327</v>
+        <v>571325</v>
       </c>
       <c r="R25" t="n">
-        <v>6465739</v>
+        <v>6465727</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3188,38 +3194,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129543378</v>
+        <v>129543457</v>
       </c>
       <c r="B26" t="n">
-        <v>98768</v>
+        <v>91588</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3227,10 +3232,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571325</v>
+        <v>571370</v>
       </c>
       <c r="R26" t="n">
-        <v>6465727</v>
+        <v>6465725</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3263,11 +3268,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3295,37 +3295,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543509</v>
+        <v>129543603</v>
       </c>
       <c r="B27" t="n">
-        <v>92040</v>
+        <v>57896</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3333,10 +3346,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571359</v>
+        <v>571376</v>
       </c>
       <c r="R27" t="n">
-        <v>6465750</v>
+        <v>6465679</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3373,7 +3386,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
+          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3382,7 +3395,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3401,54 +3413,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543344</v>
+        <v>129543509</v>
       </c>
       <c r="B28" t="n">
-        <v>57732</v>
+        <v>92041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3456,10 +3451,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571283</v>
+        <v>571359</v>
       </c>
       <c r="R28" t="n">
-        <v>6465682</v>
+        <v>6465750</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3496,7 +3491,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
+          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3505,6 +3500,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3523,38 +3519,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543537</v>
+        <v>129543344</v>
       </c>
       <c r="B29" t="n">
-        <v>98768</v>
+        <v>57733</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3562,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571452</v>
+        <v>571283</v>
       </c>
       <c r="R29" t="n">
-        <v>6465730</v>
+        <v>6465682</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,7 +3614,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3611,7 +3623,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3630,50 +3641,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543603</v>
+        <v>129543537</v>
       </c>
       <c r="B30" t="n">
-        <v>57895</v>
+        <v>98769</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3681,10 +3680,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571376</v>
+        <v>571452</v>
       </c>
       <c r="R30" t="n">
-        <v>6465679</v>
+        <v>6465730</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3721,7 +3720,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3730,6 +3729,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3748,37 +3748,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129543655</v>
+        <v>129543678</v>
       </c>
       <c r="B31" t="n">
-        <v>79694</v>
+        <v>98769</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3786,10 +3787,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571375</v>
+        <v>571480</v>
       </c>
       <c r="R31" t="n">
-        <v>6465649</v>
+        <v>6465780</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3822,6 +3823,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3849,10 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543678</v>
+        <v>129543442</v>
       </c>
       <c r="B32" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,10 +3894,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571480</v>
+        <v>571390</v>
       </c>
       <c r="R32" t="n">
-        <v>6465780</v>
+        <v>6465781</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3956,38 +3962,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543442</v>
+        <v>129543655</v>
       </c>
       <c r="B33" t="n">
-        <v>98768</v>
+        <v>79695</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3995,10 +4000,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571390</v>
+        <v>571375</v>
       </c>
       <c r="R33" t="n">
-        <v>6465781</v>
+        <v>6465649</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4031,11 +4036,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4066,7 +4066,7 @@
         <v>129543686</v>
       </c>
       <c r="B34" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>129543389</v>
       </c>
       <c r="B35" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>129543685</v>
       </c>
       <c r="B36" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>129543368</v>
       </c>
       <c r="B37" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4491,10 +4491,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129543651</v>
+        <v>129543564</v>
       </c>
       <c r="B38" t="n">
-        <v>79694</v>
+        <v>91588</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4502,21 +4502,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>571336</v>
+        <v>571443</v>
       </c>
       <c r="R38" t="n">
-        <v>6465638</v>
+        <v>6465681</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4592,38 +4592,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543356</v>
+        <v>129543651</v>
       </c>
       <c r="B39" t="n">
-        <v>98768</v>
+        <v>79695</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4631,10 +4630,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571315</v>
+        <v>571336</v>
       </c>
       <c r="R39" t="n">
-        <v>6465727</v>
+        <v>6465638</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4667,11 +4666,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4699,10 +4693,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543624</v>
+        <v>129543356</v>
       </c>
       <c r="B40" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4738,10 +4732,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571370</v>
+        <v>571315</v>
       </c>
       <c r="R40" t="n">
-        <v>6465662</v>
+        <v>6465727</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4778,7 +4772,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ett tiotal</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4809,7 +4803,7 @@
         <v>129543361</v>
       </c>
       <c r="B41" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4913,37 +4907,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543564</v>
+        <v>129543624</v>
       </c>
       <c r="B42" t="n">
-        <v>91587</v>
+        <v>98769</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4951,10 +4946,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571443</v>
+        <v>571370</v>
       </c>
       <c r="R42" t="n">
-        <v>6465681</v>
+        <v>6465662</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4987,6 +4982,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5017,7 +5017,7 @@
         <v>129543662</v>
       </c>
       <c r="B43" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>129543395</v>
       </c>
       <c r="B44" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>129741149</v>
       </c>
       <c r="B45" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>129741141</v>
       </c>
       <c r="B46" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -2451,32 +2451,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129543392</v>
+        <v>129543383</v>
       </c>
       <c r="B19" t="n">
-        <v>98769</v>
+        <v>105835</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2490,10 +2490,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571309</v>
+        <v>571325</v>
       </c>
       <c r="R19" t="n">
-        <v>6465740</v>
+        <v>6465727</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2558,32 +2558,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129543383</v>
+        <v>129543392</v>
       </c>
       <c r="B20" t="n">
-        <v>105835</v>
+        <v>98769</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571325</v>
+        <v>571309</v>
       </c>
       <c r="R20" t="n">
-        <v>6465727</v>
+        <v>6465740</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ett tjugotal</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3295,50 +3295,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543603</v>
+        <v>129543509</v>
       </c>
       <c r="B27" t="n">
-        <v>57896</v>
+        <v>92041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3346,10 +3333,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571376</v>
+        <v>571359</v>
       </c>
       <c r="R27" t="n">
-        <v>6465679</v>
+        <v>6465750</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3386,7 +3373,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
+          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3395,6 +3382,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3413,37 +3401,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543509</v>
+        <v>129543344</v>
       </c>
       <c r="B28" t="n">
-        <v>92041</v>
+        <v>57733</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3451,10 +3456,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571359</v>
+        <v>571283</v>
       </c>
       <c r="R28" t="n">
-        <v>6465750</v>
+        <v>6465682</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3491,7 +3496,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
+          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3500,7 +3505,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3519,10 +3523,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543344</v>
+        <v>129543603</v>
       </c>
       <c r="B29" t="n">
-        <v>57733</v>
+        <v>57896</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3530,26 +3534,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3557,11 +3561,7 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571283</v>
+        <v>571376</v>
       </c>
       <c r="R29" t="n">
-        <v>6465682</v>
+        <v>6465679</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
+          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>129543469</v>
       </c>
       <c r="B5" t="n">
-        <v>96211</v>
+        <v>96216</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>129543327</v>
       </c>
       <c r="B6" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>129543544</v>
       </c>
       <c r="B7" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
         <v>129543463</v>
       </c>
       <c r="B8" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1415,38 +1415,39 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543522</v>
+        <v>129543448</v>
       </c>
       <c r="B9" t="n">
-        <v>98769</v>
+        <v>4773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1454,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571382</v>
+        <v>571395</v>
       </c>
       <c r="R9" t="n">
-        <v>6465758</v>
+        <v>6465767</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1491,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129543430</v>
+        <v>129543522</v>
       </c>
       <c r="B10" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1561,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571367</v>
+        <v>571382</v>
       </c>
       <c r="R10" t="n">
-        <v>6465787</v>
+        <v>6465758</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,39 +1625,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543448</v>
+        <v>129543430</v>
       </c>
       <c r="B11" t="n">
-        <v>4773</v>
+        <v>98774</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1669,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571395</v>
+        <v>571367</v>
       </c>
       <c r="R11" t="n">
-        <v>6465767</v>
+        <v>6465787</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,6 +1700,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1735,7 @@
         <v>129543553</v>
       </c>
       <c r="B12" t="n">
-        <v>91602</v>
+        <v>91607</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>129543434</v>
       </c>
       <c r="B13" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>129543516</v>
       </c>
       <c r="B14" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>129543475</v>
       </c>
       <c r="B15" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>129543571</v>
       </c>
       <c r="B16" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2249,10 +2249,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543452</v>
+        <v>129543676</v>
       </c>
       <c r="B17" t="n">
-        <v>92230</v>
+        <v>91593</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2260,21 +2260,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5454</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571381</v>
+        <v>571480</v>
       </c>
       <c r="R17" t="n">
-        <v>6465712</v>
+        <v>6465733</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543676</v>
+        <v>129543452</v>
       </c>
       <c r="B18" t="n">
-        <v>91588</v>
+        <v>92235</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,21 +2361,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5454</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571480</v>
+        <v>571381</v>
       </c>
       <c r="R18" t="n">
-        <v>6465733</v>
+        <v>6465712</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,7 +2454,7 @@
         <v>129543383</v>
       </c>
       <c r="B19" t="n">
-        <v>105835</v>
+        <v>105840</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>129543392</v>
       </c>
       <c r="B20" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>129543658</v>
       </c>
       <c r="B21" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129543526</v>
       </c>
       <c r="B22" t="n">
-        <v>105835</v>
+        <v>105840</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>129543484</v>
       </c>
       <c r="B23" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>129543348</v>
       </c>
       <c r="B24" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3087,38 +3087,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543378</v>
+        <v>129543457</v>
       </c>
       <c r="B25" t="n">
-        <v>98769</v>
+        <v>91593</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3126,10 +3125,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571325</v>
+        <v>571370</v>
       </c>
       <c r="R25" t="n">
-        <v>6465727</v>
+        <v>6465725</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3162,11 +3161,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3194,37 +3188,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129543457</v>
+        <v>129543378</v>
       </c>
       <c r="B26" t="n">
-        <v>91588</v>
+        <v>98774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3232,10 +3227,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571370</v>
+        <v>571325</v>
       </c>
       <c r="R26" t="n">
-        <v>6465725</v>
+        <v>6465727</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3268,6 +3263,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3298,7 +3298,7 @@
         <v>129543509</v>
       </c>
       <c r="B27" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3401,10 +3401,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543344</v>
+        <v>129543603</v>
       </c>
       <c r="B28" t="n">
-        <v>57733</v>
+        <v>57896</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3412,26 +3412,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3439,11 +3439,7 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -3456,10 +3452,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571283</v>
+        <v>571376</v>
       </c>
       <c r="R28" t="n">
-        <v>6465682</v>
+        <v>6465679</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3496,7 +3492,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
+          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3523,10 +3519,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543603</v>
+        <v>129543344</v>
       </c>
       <c r="B29" t="n">
-        <v>57896</v>
+        <v>57733</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3534,26 +3530,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3561,7 +3557,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571376</v>
+        <v>571283</v>
       </c>
       <c r="R29" t="n">
-        <v>6465679</v>
+        <v>6465682</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
+          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3644,7 +3644,7 @@
         <v>129543537</v>
       </c>
       <c r="B30" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3748,38 +3748,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129543678</v>
+        <v>129543655</v>
       </c>
       <c r="B31" t="n">
-        <v>98769</v>
+        <v>79700</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3787,10 +3786,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571480</v>
+        <v>571375</v>
       </c>
       <c r="R31" t="n">
-        <v>6465780</v>
+        <v>6465649</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3823,11 +3822,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,10 +3849,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543442</v>
+        <v>129543678</v>
       </c>
       <c r="B32" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3894,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571390</v>
+        <v>571480</v>
       </c>
       <c r="R32" t="n">
-        <v>6465781</v>
+        <v>6465780</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3962,37 +3956,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543655</v>
+        <v>129543442</v>
       </c>
       <c r="B33" t="n">
-        <v>79695</v>
+        <v>98774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4000,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571375</v>
+        <v>571390</v>
       </c>
       <c r="R33" t="n">
-        <v>6465649</v>
+        <v>6465781</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4036,6 +4031,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4066,7 +4066,7 @@
         <v>129543686</v>
       </c>
       <c r="B34" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,10 +4170,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543389</v>
+        <v>129543685</v>
       </c>
       <c r="B35" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>571323</v>
+        <v>571461</v>
       </c>
       <c r="R35" t="n">
-        <v>6465742</v>
+        <v>6465806</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ett tjugotal</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4277,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129543685</v>
+        <v>129543389</v>
       </c>
       <c r="B36" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>571461</v>
+        <v>571323</v>
       </c>
       <c r="R36" t="n">
-        <v>6465806</v>
+        <v>6465742</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4387,7 +4387,7 @@
         <v>129543368</v>
       </c>
       <c r="B37" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4491,37 +4491,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129543564</v>
+        <v>129543356</v>
       </c>
       <c r="B38" t="n">
-        <v>91588</v>
+        <v>98774</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4529,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>571443</v>
+        <v>571315</v>
       </c>
       <c r="R38" t="n">
-        <v>6465681</v>
+        <v>6465727</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,6 +4566,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4592,37 +4598,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543651</v>
+        <v>129543361</v>
       </c>
       <c r="B39" t="n">
-        <v>79695</v>
+        <v>98774</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4630,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571336</v>
+        <v>571328</v>
       </c>
       <c r="R39" t="n">
-        <v>6465638</v>
+        <v>6465727</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4666,6 +4673,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4693,10 +4705,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543356</v>
+        <v>129543624</v>
       </c>
       <c r="B40" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4732,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571315</v>
+        <v>571370</v>
       </c>
       <c r="R40" t="n">
-        <v>6465727</v>
+        <v>6465662</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4772,7 +4784,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4800,38 +4812,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543361</v>
+        <v>129543564</v>
       </c>
       <c r="B41" t="n">
-        <v>98769</v>
+        <v>91593</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4839,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571328</v>
+        <v>571443</v>
       </c>
       <c r="R41" t="n">
-        <v>6465727</v>
+        <v>6465681</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4875,11 +4886,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4907,38 +4913,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543624</v>
+        <v>129543651</v>
       </c>
       <c r="B42" t="n">
-        <v>98769</v>
+        <v>79700</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4946,10 +4951,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571370</v>
+        <v>571336</v>
       </c>
       <c r="R42" t="n">
-        <v>6465662</v>
+        <v>6465638</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4982,11 +4987,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5017,7 +5017,7 @@
         <v>129543662</v>
       </c>
       <c r="B43" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>129543395</v>
       </c>
       <c r="B44" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -1100,7 +1100,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543327</v>
+        <v>129543544</v>
       </c>
       <c r="B6" t="n">
         <v>98774</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571291</v>
+        <v>571456</v>
       </c>
       <c r="R6" t="n">
-        <v>6465665</v>
+        <v>6465730</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543544</v>
+        <v>129543327</v>
       </c>
       <c r="B7" t="n">
         <v>98774</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571456</v>
+        <v>571291</v>
       </c>
       <c r="R7" t="n">
-        <v>6465730</v>
+        <v>6465665</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129543522</v>
+        <v>129543430</v>
       </c>
       <c r="B10" t="n">
         <v>98774</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571382</v>
+        <v>571367</v>
       </c>
       <c r="R10" t="n">
-        <v>6465758</v>
+        <v>6465787</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,7 +1625,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543430</v>
+        <v>129543522</v>
       </c>
       <c r="B11" t="n">
         <v>98774</v>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571367</v>
+        <v>571382</v>
       </c>
       <c r="R11" t="n">
-        <v>6465787</v>
+        <v>6465758</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,10 +1732,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129543553</v>
+        <v>129543434</v>
       </c>
       <c r="B12" t="n">
-        <v>91607</v>
+        <v>91593</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1743,21 +1743,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571453</v>
+        <v>571376</v>
       </c>
       <c r="R12" t="n">
-        <v>6465695</v>
+        <v>6465781</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129543434</v>
+        <v>129543553</v>
       </c>
       <c r="B13" t="n">
-        <v>91593</v>
+        <v>91607</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,21 +1844,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571376</v>
+        <v>571453</v>
       </c>
       <c r="R13" t="n">
-        <v>6465781</v>
+        <v>6465695</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2873,38 +2873,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129543484</v>
+        <v>129543457</v>
       </c>
       <c r="B23" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2912,10 +2911,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>571327</v>
+        <v>571370</v>
       </c>
       <c r="R23" t="n">
-        <v>6465739</v>
+        <v>6465725</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2948,11 +2947,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2980,7 +2974,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129543348</v>
+        <v>129543484</v>
       </c>
       <c r="B24" t="n">
         <v>98774</v>
@@ -3019,10 +3013,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571288</v>
+        <v>571327</v>
       </c>
       <c r="R24" t="n">
-        <v>6465690</v>
+        <v>6465739</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3087,37 +3081,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543457</v>
+        <v>129543348</v>
       </c>
       <c r="B25" t="n">
-        <v>91593</v>
+        <v>98774</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3125,10 +3120,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571370</v>
+        <v>571288</v>
       </c>
       <c r="R25" t="n">
-        <v>6465725</v>
+        <v>6465690</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3161,6 +3156,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3401,10 +3401,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543603</v>
+        <v>129543344</v>
       </c>
       <c r="B28" t="n">
-        <v>57896</v>
+        <v>57733</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3412,26 +3412,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3439,7 +3439,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -3452,10 +3456,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571376</v>
+        <v>571283</v>
       </c>
       <c r="R28" t="n">
-        <v>6465679</v>
+        <v>6465682</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3492,7 +3496,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
+          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3519,10 +3523,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543344</v>
+        <v>129543603</v>
       </c>
       <c r="B29" t="n">
-        <v>57733</v>
+        <v>57896</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3530,26 +3534,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3557,11 +3561,7 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571283</v>
+        <v>571376</v>
       </c>
       <c r="R29" t="n">
-        <v>6465682</v>
+        <v>6465679</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
+          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3849,7 +3849,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543678</v>
+        <v>129543442</v>
       </c>
       <c r="B32" t="n">
         <v>98774</v>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571480</v>
+        <v>571390</v>
       </c>
       <c r="R32" t="n">
-        <v>6465780</v>
+        <v>6465781</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3956,7 +3956,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543442</v>
+        <v>129543678</v>
       </c>
       <c r="B33" t="n">
         <v>98774</v>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571390</v>
+        <v>571480</v>
       </c>
       <c r="R33" t="n">
-        <v>6465781</v>
+        <v>6465780</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4170,7 +4170,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129543685</v>
+        <v>129543389</v>
       </c>
       <c r="B35" t="n">
         <v>98774</v>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>571461</v>
+        <v>571323</v>
       </c>
       <c r="R35" t="n">
-        <v>6465806</v>
+        <v>6465742</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4277,7 +4277,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129543389</v>
+        <v>129543685</v>
       </c>
       <c r="B36" t="n">
         <v>98774</v>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>571323</v>
+        <v>571461</v>
       </c>
       <c r="R36" t="n">
-        <v>6465742</v>
+        <v>6465806</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ett tjugotal</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4491,38 +4491,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129543356</v>
+        <v>129543564</v>
       </c>
       <c r="B38" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4530,10 +4529,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>571315</v>
+        <v>571443</v>
       </c>
       <c r="R38" t="n">
-        <v>6465727</v>
+        <v>6465681</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,11 +4565,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4598,38 +4592,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543361</v>
+        <v>129543651</v>
       </c>
       <c r="B39" t="n">
-        <v>98774</v>
+        <v>79700</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4637,10 +4630,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571328</v>
+        <v>571336</v>
       </c>
       <c r="R39" t="n">
-        <v>6465727</v>
+        <v>6465638</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4673,11 +4666,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4705,7 +4693,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543624</v>
+        <v>129543356</v>
       </c>
       <c r="B40" t="n">
         <v>98774</v>
@@ -4744,10 +4732,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571370</v>
+        <v>571315</v>
       </c>
       <c r="R40" t="n">
-        <v>6465662</v>
+        <v>6465727</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4784,7 +4772,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ett tiotal</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4812,37 +4800,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543564</v>
+        <v>129543361</v>
       </c>
       <c r="B41" t="n">
-        <v>91593</v>
+        <v>98774</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4850,10 +4839,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571443</v>
+        <v>571328</v>
       </c>
       <c r="R41" t="n">
-        <v>6465681</v>
+        <v>6465727</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,6 +4875,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4913,37 +4907,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543651</v>
+        <v>129543624</v>
       </c>
       <c r="B42" t="n">
-        <v>79700</v>
+        <v>98774</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4951,10 +4946,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571336</v>
+        <v>571370</v>
       </c>
       <c r="R42" t="n">
-        <v>6465638</v>
+        <v>6465662</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4987,6 +4982,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -1100,7 +1100,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543544</v>
+        <v>129543327</v>
       </c>
       <c r="B6" t="n">
         <v>98774</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571456</v>
+        <v>571291</v>
       </c>
       <c r="R6" t="n">
-        <v>6465730</v>
+        <v>6465665</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543327</v>
+        <v>129543544</v>
       </c>
       <c r="B7" t="n">
         <v>98774</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571291</v>
+        <v>571456</v>
       </c>
       <c r="R7" t="n">
-        <v>6465665</v>
+        <v>6465730</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129543430</v>
+        <v>129543522</v>
       </c>
       <c r="B10" t="n">
         <v>98774</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571367</v>
+        <v>571382</v>
       </c>
       <c r="R10" t="n">
-        <v>6465787</v>
+        <v>6465758</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,7 +1625,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543522</v>
+        <v>129543430</v>
       </c>
       <c r="B11" t="n">
         <v>98774</v>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571382</v>
+        <v>571367</v>
       </c>
       <c r="R11" t="n">
-        <v>6465758</v>
+        <v>6465787</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,10 +1732,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129543434</v>
+        <v>129543553</v>
       </c>
       <c r="B12" t="n">
-        <v>91593</v>
+        <v>91607</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1743,21 +1743,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571376</v>
+        <v>571453</v>
       </c>
       <c r="R12" t="n">
-        <v>6465781</v>
+        <v>6465695</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129543553</v>
+        <v>129543434</v>
       </c>
       <c r="B13" t="n">
-        <v>91607</v>
+        <v>91593</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,21 +1844,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571453</v>
+        <v>571376</v>
       </c>
       <c r="R13" t="n">
-        <v>6465695</v>
+        <v>6465781</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2974,7 +2974,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129543484</v>
+        <v>129543348</v>
       </c>
       <c r="B24" t="n">
         <v>98774</v>
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571327</v>
+        <v>571288</v>
       </c>
       <c r="R24" t="n">
-        <v>6465739</v>
+        <v>6465690</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,7 +3081,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543348</v>
+        <v>129543378</v>
       </c>
       <c r="B25" t="n">
         <v>98774</v>
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571288</v>
+        <v>571325</v>
       </c>
       <c r="R25" t="n">
-        <v>6465690</v>
+        <v>6465727</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129543378</v>
+        <v>129543484</v>
       </c>
       <c r="B26" t="n">
         <v>98774</v>
@@ -3227,10 +3227,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571325</v>
+        <v>571327</v>
       </c>
       <c r="R26" t="n">
-        <v>6465727</v>
+        <v>6465739</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3295,37 +3295,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543509</v>
+        <v>129543344</v>
       </c>
       <c r="B27" t="n">
-        <v>92046</v>
+        <v>57733</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3333,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571359</v>
+        <v>571283</v>
       </c>
       <c r="R27" t="n">
-        <v>6465750</v>
+        <v>6465682</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3373,7 +3390,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
+          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3382,7 +3399,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3401,10 +3417,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543344</v>
+        <v>129543603</v>
       </c>
       <c r="B28" t="n">
-        <v>57733</v>
+        <v>57896</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3412,26 +3428,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3439,11 +3455,7 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -3456,10 +3468,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571283</v>
+        <v>571376</v>
       </c>
       <c r="R28" t="n">
-        <v>6465682</v>
+        <v>6465679</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3496,7 +3508,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
+          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3523,50 +3535,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543603</v>
+        <v>129543509</v>
       </c>
       <c r="B29" t="n">
-        <v>57896</v>
+        <v>92046</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3574,10 +3573,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571376</v>
+        <v>571359</v>
       </c>
       <c r="R29" t="n">
-        <v>6465679</v>
+        <v>6465750</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,7 +3613,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
+          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3623,6 +3622,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3748,37 +3748,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129543655</v>
+        <v>129543678</v>
       </c>
       <c r="B31" t="n">
-        <v>79700</v>
+        <v>98774</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3786,10 +3787,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571375</v>
+        <v>571480</v>
       </c>
       <c r="R31" t="n">
-        <v>6465649</v>
+        <v>6465780</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3822,6 +3823,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3849,38 +3855,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543442</v>
+        <v>129543655</v>
       </c>
       <c r="B32" t="n">
-        <v>98774</v>
+        <v>79700</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3888,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571390</v>
+        <v>571375</v>
       </c>
       <c r="R32" t="n">
-        <v>6465781</v>
+        <v>6465649</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3924,11 +3929,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3956,7 +3956,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543678</v>
+        <v>129543442</v>
       </c>
       <c r="B33" t="n">
         <v>98774</v>
@@ -3995,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571480</v>
+        <v>571390</v>
       </c>
       <c r="R33" t="n">
-        <v>6465780</v>
+        <v>6465781</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -1314,37 +1314,39 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543463</v>
+        <v>129543448</v>
       </c>
       <c r="B8" t="n">
-        <v>79700</v>
+        <v>4773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1352,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571341</v>
+        <v>571395</v>
       </c>
       <c r="R8" t="n">
-        <v>6465672</v>
+        <v>6465767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,39 +1417,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543448</v>
+        <v>129543522</v>
       </c>
       <c r="B9" t="n">
-        <v>4773</v>
+        <v>98774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1455,10 +1456,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571395</v>
+        <v>571382</v>
       </c>
       <c r="R9" t="n">
-        <v>6465767</v>
+        <v>6465758</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,6 +1492,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1518,7 +1524,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129543522</v>
+        <v>129543430</v>
       </c>
       <c r="B10" t="n">
         <v>98774</v>
@@ -1557,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571382</v>
+        <v>571367</v>
       </c>
       <c r="R10" t="n">
-        <v>6465758</v>
+        <v>6465787</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,38 +1631,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543430</v>
+        <v>129543463</v>
       </c>
       <c r="B11" t="n">
-        <v>98774</v>
+        <v>79700</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1664,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571367</v>
+        <v>571341</v>
       </c>
       <c r="R11" t="n">
-        <v>6465787</v>
+        <v>6465672</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,11 +1705,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2249,10 +2249,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543676</v>
+        <v>129543452</v>
       </c>
       <c r="B17" t="n">
-        <v>91593</v>
+        <v>92235</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2260,21 +2260,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5454</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571480</v>
+        <v>571381</v>
       </c>
       <c r="R17" t="n">
-        <v>6465733</v>
+        <v>6465712</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543452</v>
+        <v>129543676</v>
       </c>
       <c r="B18" t="n">
-        <v>92235</v>
+        <v>91593</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,21 +2361,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5454</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571381</v>
+        <v>571480</v>
       </c>
       <c r="R18" t="n">
-        <v>6465712</v>
+        <v>6465733</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2974,7 +2974,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129543348</v>
+        <v>129543484</v>
       </c>
       <c r="B24" t="n">
         <v>98774</v>
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>571288</v>
+        <v>571327</v>
       </c>
       <c r="R24" t="n">
-        <v>6465690</v>
+        <v>6465739</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3081,7 +3081,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129543378</v>
+        <v>129543348</v>
       </c>
       <c r="B25" t="n">
         <v>98774</v>
@@ -3120,10 +3120,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>571325</v>
+        <v>571288</v>
       </c>
       <c r="R25" t="n">
-        <v>6465727</v>
+        <v>6465690</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129543484</v>
+        <v>129543378</v>
       </c>
       <c r="B26" t="n">
         <v>98774</v>
@@ -3227,10 +3227,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>571327</v>
+        <v>571325</v>
       </c>
       <c r="R26" t="n">
-        <v>6465739</v>
+        <v>6465727</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3295,54 +3295,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543344</v>
+        <v>129543537</v>
       </c>
       <c r="B27" t="n">
-        <v>57733</v>
+        <v>98774</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3350,10 +3334,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571283</v>
+        <v>571452</v>
       </c>
       <c r="R27" t="n">
-        <v>6465682</v>
+        <v>6465730</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3390,7 +3374,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3399,6 +3383,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3417,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543603</v>
+        <v>129543344</v>
       </c>
       <c r="B28" t="n">
-        <v>57896</v>
+        <v>57733</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3428,26 +3413,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3455,7 +3440,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -3468,10 +3457,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571376</v>
+        <v>571283</v>
       </c>
       <c r="R28" t="n">
-        <v>6465679</v>
+        <v>6465682</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3508,7 +3497,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
+          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3641,38 +3630,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543537</v>
+        <v>129543603</v>
       </c>
       <c r="B30" t="n">
-        <v>98774</v>
+        <v>57896</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3680,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571452</v>
+        <v>571376</v>
       </c>
       <c r="R30" t="n">
-        <v>6465730</v>
+        <v>6465679</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3720,7 +3721,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3729,7 +3730,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3748,38 +3748,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129543678</v>
+        <v>129543655</v>
       </c>
       <c r="B31" t="n">
-        <v>98774</v>
+        <v>79700</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3787,10 +3786,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571480</v>
+        <v>571375</v>
       </c>
       <c r="R31" t="n">
-        <v>6465780</v>
+        <v>6465649</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3823,11 +3822,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,37 +3849,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543655</v>
+        <v>129543678</v>
       </c>
       <c r="B32" t="n">
-        <v>79700</v>
+        <v>98774</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3893,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571375</v>
+        <v>571480</v>
       </c>
       <c r="R32" t="n">
-        <v>6465649</v>
+        <v>6465780</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3929,6 +3924,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4491,10 +4491,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129543564</v>
+        <v>129543651</v>
       </c>
       <c r="B38" t="n">
-        <v>91593</v>
+        <v>79700</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4502,21 +4502,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>571443</v>
+        <v>571336</v>
       </c>
       <c r="R38" t="n">
-        <v>6465681</v>
+        <v>6465638</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4592,10 +4592,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543651</v>
+        <v>129543564</v>
       </c>
       <c r="B39" t="n">
-        <v>79700</v>
+        <v>91593</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4603,21 +4603,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4630,10 +4630,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571336</v>
+        <v>571443</v>
       </c>
       <c r="R39" t="n">
-        <v>6465638</v>
+        <v>6465681</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>129543469</v>
       </c>
       <c r="B5" t="n">
-        <v>96216</v>
+        <v>96220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>129543327</v>
       </c>
       <c r="B6" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>129543544</v>
       </c>
       <c r="B7" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,39 +1314,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543448</v>
+        <v>129543463</v>
       </c>
       <c r="B8" t="n">
-        <v>4773</v>
+        <v>79700</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1354,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571395</v>
+        <v>571341</v>
       </c>
       <c r="R8" t="n">
-        <v>6465767</v>
+        <v>6465672</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,7 +1418,7 @@
         <v>129543522</v>
       </c>
       <c r="B9" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1527,7 +1525,7 @@
         <v>129543430</v>
       </c>
       <c r="B10" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,37 +1629,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543463</v>
+        <v>129543448</v>
       </c>
       <c r="B11" t="n">
-        <v>79700</v>
+        <v>4773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571341</v>
+        <v>571395</v>
       </c>
       <c r="R11" t="n">
-        <v>6465672</v>
+        <v>6465767</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1732,10 +1732,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129543553</v>
+        <v>129543434</v>
       </c>
       <c r="B12" t="n">
-        <v>91607</v>
+        <v>91597</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1743,21 +1743,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571453</v>
+        <v>571376</v>
       </c>
       <c r="R12" t="n">
-        <v>6465695</v>
+        <v>6465781</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129543434</v>
+        <v>129543553</v>
       </c>
       <c r="B13" t="n">
-        <v>91593</v>
+        <v>91611</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,21 +1844,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571376</v>
+        <v>571453</v>
       </c>
       <c r="R13" t="n">
-        <v>6465781</v>
+        <v>6465695</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,7 +1937,7 @@
         <v>129543516</v>
       </c>
       <c r="B14" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>129543475</v>
       </c>
       <c r="B15" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>129543571</v>
       </c>
       <c r="B16" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2249,10 +2249,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543452</v>
+        <v>129543676</v>
       </c>
       <c r="B17" t="n">
-        <v>92235</v>
+        <v>91597</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2260,21 +2260,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5454</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571381</v>
+        <v>571480</v>
       </c>
       <c r="R17" t="n">
-        <v>6465712</v>
+        <v>6465733</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543676</v>
+        <v>129543452</v>
       </c>
       <c r="B18" t="n">
-        <v>91593</v>
+        <v>92239</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,21 +2361,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5454</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571480</v>
+        <v>571381</v>
       </c>
       <c r="R18" t="n">
-        <v>6465733</v>
+        <v>6465712</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,7 +2454,7 @@
         <v>129543383</v>
       </c>
       <c r="B19" t="n">
-        <v>105840</v>
+        <v>105844</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>129543392</v>
       </c>
       <c r="B20" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>129543658</v>
       </c>
       <c r="B21" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129543526</v>
       </c>
       <c r="B22" t="n">
-        <v>105840</v>
+        <v>105844</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>129543457</v>
       </c>
       <c r="B23" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>129543484</v>
       </c>
       <c r="B24" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>129543348</v>
       </c>
       <c r="B25" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>129543378</v>
       </c>
       <c r="B26" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3295,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543537</v>
+        <v>129543509</v>
       </c>
       <c r="B27" t="n">
-        <v>98774</v>
+        <v>92050</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3306,27 +3306,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3334,10 +3333,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571452</v>
+        <v>571359</v>
       </c>
       <c r="R27" t="n">
-        <v>6465730</v>
+        <v>6465750</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3374,7 +3373,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3524,37 +3523,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543509</v>
+        <v>129543603</v>
       </c>
       <c r="B29" t="n">
-        <v>92046</v>
+        <v>57896</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3562,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571359</v>
+        <v>571376</v>
       </c>
       <c r="R29" t="n">
-        <v>6465750</v>
+        <v>6465679</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3602,7 +3614,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
+          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3611,7 +3623,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3630,50 +3641,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543603</v>
+        <v>129543537</v>
       </c>
       <c r="B30" t="n">
-        <v>57896</v>
+        <v>98778</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3681,10 +3680,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571376</v>
+        <v>571452</v>
       </c>
       <c r="R30" t="n">
-        <v>6465679</v>
+        <v>6465730</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3721,7 +3720,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3730,6 +3729,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3748,37 +3748,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129543655</v>
+        <v>129543678</v>
       </c>
       <c r="B31" t="n">
-        <v>79700</v>
+        <v>98778</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3786,10 +3787,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571375</v>
+        <v>571480</v>
       </c>
       <c r="R31" t="n">
-        <v>6465649</v>
+        <v>6465780</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3822,6 +3823,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3849,10 +3855,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543678</v>
+        <v>129543442</v>
       </c>
       <c r="B32" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3888,10 +3894,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571480</v>
+        <v>571390</v>
       </c>
       <c r="R32" t="n">
-        <v>6465780</v>
+        <v>6465781</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3956,38 +3962,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543442</v>
+        <v>129543655</v>
       </c>
       <c r="B33" t="n">
-        <v>98774</v>
+        <v>79700</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3995,10 +4000,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571390</v>
+        <v>571375</v>
       </c>
       <c r="R33" t="n">
-        <v>6465781</v>
+        <v>6465649</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4031,11 +4036,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4066,7 +4066,7 @@
         <v>129543686</v>
       </c>
       <c r="B34" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>129543389</v>
       </c>
       <c r="B35" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>129543685</v>
       </c>
       <c r="B36" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>129543368</v>
       </c>
       <c r="B37" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4491,37 +4491,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129543651</v>
+        <v>129543356</v>
       </c>
       <c r="B38" t="n">
-        <v>79700</v>
+        <v>98778</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4529,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>571336</v>
+        <v>571315</v>
       </c>
       <c r="R38" t="n">
-        <v>6465638</v>
+        <v>6465727</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,6 +4566,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4592,37 +4598,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543564</v>
+        <v>129543361</v>
       </c>
       <c r="B39" t="n">
-        <v>91593</v>
+        <v>98778</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4630,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571443</v>
+        <v>571328</v>
       </c>
       <c r="R39" t="n">
-        <v>6465681</v>
+        <v>6465727</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4666,6 +4673,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4693,10 +4705,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543356</v>
+        <v>129543624</v>
       </c>
       <c r="B40" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4732,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571315</v>
+        <v>571370</v>
       </c>
       <c r="R40" t="n">
-        <v>6465727</v>
+        <v>6465662</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4772,7 +4784,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4800,38 +4812,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543361</v>
+        <v>129543564</v>
       </c>
       <c r="B41" t="n">
-        <v>98774</v>
+        <v>91597</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4839,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571328</v>
+        <v>571443</v>
       </c>
       <c r="R41" t="n">
-        <v>6465727</v>
+        <v>6465681</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4875,11 +4886,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4907,38 +4913,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543624</v>
+        <v>129543651</v>
       </c>
       <c r="B42" t="n">
-        <v>98774</v>
+        <v>79700</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4946,10 +4951,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571370</v>
+        <v>571336</v>
       </c>
       <c r="R42" t="n">
-        <v>6465662</v>
+        <v>6465638</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4982,11 +4987,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5017,7 +5017,7 @@
         <v>129543662</v>
       </c>
       <c r="B43" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>129543395</v>
       </c>
       <c r="B44" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>129543469</v>
       </c>
       <c r="B5" t="n">
-        <v>96220</v>
+        <v>96222</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543327</v>
+        <v>129543544</v>
       </c>
       <c r="B6" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571291</v>
+        <v>571456</v>
       </c>
       <c r="R6" t="n">
-        <v>6465665</v>
+        <v>6465730</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543544</v>
+        <v>129543327</v>
       </c>
       <c r="B7" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571456</v>
+        <v>571291</v>
       </c>
       <c r="R7" t="n">
-        <v>6465730</v>
+        <v>6465665</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1415,38 +1415,39 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543522</v>
+        <v>129543448</v>
       </c>
       <c r="B9" t="n">
-        <v>98778</v>
+        <v>4773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1454,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571382</v>
+        <v>571395</v>
       </c>
       <c r="R9" t="n">
-        <v>6465758</v>
+        <v>6465767</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1491,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1525,7 +1521,7 @@
         <v>129543430</v>
       </c>
       <c r="B10" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1629,39 +1625,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543448</v>
+        <v>129543522</v>
       </c>
       <c r="B11" t="n">
-        <v>4773</v>
+        <v>98780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1669,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571395</v>
+        <v>571382</v>
       </c>
       <c r="R11" t="n">
-        <v>6465767</v>
+        <v>6465758</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,6 +1700,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1735,7 @@
         <v>129543434</v>
       </c>
       <c r="B12" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>129543553</v>
       </c>
       <c r="B13" t="n">
-        <v>91611</v>
+        <v>91613</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>129543516</v>
       </c>
       <c r="B14" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>129543475</v>
       </c>
       <c r="B15" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>129543571</v>
       </c>
       <c r="B16" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>129543676</v>
       </c>
       <c r="B17" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>129543452</v>
       </c>
       <c r="B18" t="n">
-        <v>92239</v>
+        <v>92241</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2451,32 +2451,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129543383</v>
+        <v>129543392</v>
       </c>
       <c r="B19" t="n">
-        <v>105844</v>
+        <v>98780</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2490,10 +2490,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571325</v>
+        <v>571309</v>
       </c>
       <c r="R19" t="n">
-        <v>6465727</v>
+        <v>6465740</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ett tjugotal</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2558,32 +2558,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129543392</v>
+        <v>129543383</v>
       </c>
       <c r="B20" t="n">
-        <v>98778</v>
+        <v>105846</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571309</v>
+        <v>571325</v>
       </c>
       <c r="R20" t="n">
-        <v>6465740</v>
+        <v>6465727</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2668,7 +2668,7 @@
         <v>129543658</v>
       </c>
       <c r="B21" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129543526</v>
       </c>
       <c r="B22" t="n">
-        <v>105844</v>
+        <v>105846</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>129543457</v>
       </c>
       <c r="B23" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>129543484</v>
       </c>
       <c r="B24" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>129543348</v>
       </c>
       <c r="B25" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>129543378</v>
       </c>
       <c r="B26" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3295,37 +3295,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543509</v>
+        <v>129543344</v>
       </c>
       <c r="B27" t="n">
-        <v>92050</v>
+        <v>57733</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3333,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571359</v>
+        <v>571283</v>
       </c>
       <c r="R27" t="n">
-        <v>6465750</v>
+        <v>6465682</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3373,7 +3390,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
+          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3382,7 +3399,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3401,54 +3417,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543344</v>
+        <v>129543509</v>
       </c>
       <c r="B28" t="n">
-        <v>57733</v>
+        <v>92052</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3456,10 +3455,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571283</v>
+        <v>571359</v>
       </c>
       <c r="R28" t="n">
-        <v>6465682</v>
+        <v>6465750</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3496,7 +3495,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
+          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3505,6 +3504,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>129543537</v>
       </c>
       <c r="B30" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>129543678</v>
       </c>
       <c r="B31" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
         <v>129543442</v>
       </c>
       <c r="B32" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4066,7 +4066,7 @@
         <v>129543686</v>
       </c>
       <c r="B34" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>129543389</v>
       </c>
       <c r="B35" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>129543685</v>
       </c>
       <c r="B36" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>129543368</v>
       </c>
       <c r="B37" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4491,38 +4491,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129543356</v>
+        <v>129543564</v>
       </c>
       <c r="B38" t="n">
-        <v>98778</v>
+        <v>91599</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4530,10 +4529,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>571315</v>
+        <v>571443</v>
       </c>
       <c r="R38" t="n">
-        <v>6465727</v>
+        <v>6465681</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,11 +4565,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4601,7 +4595,7 @@
         <v>129543361</v>
       </c>
       <c r="B39" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4705,10 +4699,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543624</v>
+        <v>129543356</v>
       </c>
       <c r="B40" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4744,10 +4738,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571370</v>
+        <v>571315</v>
       </c>
       <c r="R40" t="n">
-        <v>6465662</v>
+        <v>6465727</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4784,7 +4778,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ett tiotal</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4812,37 +4806,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543564</v>
+        <v>129543624</v>
       </c>
       <c r="B41" t="n">
-        <v>91597</v>
+        <v>98780</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4850,10 +4845,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571443</v>
+        <v>571370</v>
       </c>
       <c r="R41" t="n">
-        <v>6465681</v>
+        <v>6465662</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,6 +4881,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5017,7 +5017,7 @@
         <v>129543662</v>
       </c>
       <c r="B43" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>129543395</v>
       </c>
       <c r="B44" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -2249,37 +2249,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543676</v>
+        <v>129543392</v>
       </c>
       <c r="B17" t="n">
-        <v>91599</v>
+        <v>98780</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2287,10 +2288,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571480</v>
+        <v>571309</v>
       </c>
       <c r="R17" t="n">
-        <v>6465733</v>
+        <v>6465740</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2323,6 +2324,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2350,37 +2356,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543452</v>
+        <v>129543383</v>
       </c>
       <c r="B18" t="n">
-        <v>92241</v>
+        <v>105846</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5454</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2388,10 +2395,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571381</v>
+        <v>571325</v>
       </c>
       <c r="R18" t="n">
-        <v>6465712</v>
+        <v>6465727</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,6 +2431,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2451,38 +2463,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129543392</v>
+        <v>129543676</v>
       </c>
       <c r="B19" t="n">
-        <v>98780</v>
+        <v>91599</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2490,10 +2501,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571309</v>
+        <v>571480</v>
       </c>
       <c r="R19" t="n">
-        <v>6465740</v>
+        <v>6465733</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,11 +2537,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2558,38 +2564,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129543383</v>
+        <v>129543452</v>
       </c>
       <c r="B20" t="n">
-        <v>105846</v>
+        <v>92241</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>5454</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2597,10 +2602,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571325</v>
+        <v>571381</v>
       </c>
       <c r="R20" t="n">
-        <v>6465727</v>
+        <v>6465712</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,11 +2638,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3295,54 +3295,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543344</v>
+        <v>129543509</v>
       </c>
       <c r="B27" t="n">
-        <v>57733</v>
+        <v>92052</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3350,10 +3333,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571283</v>
+        <v>571359</v>
       </c>
       <c r="R27" t="n">
-        <v>6465682</v>
+        <v>6465750</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3390,7 +3373,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
+          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3399,6 +3382,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3417,37 +3401,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543509</v>
+        <v>129543603</v>
       </c>
       <c r="B28" t="n">
-        <v>92052</v>
+        <v>57896</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3455,10 +3452,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571359</v>
+        <v>571376</v>
       </c>
       <c r="R28" t="n">
-        <v>6465750</v>
+        <v>6465679</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3495,7 +3492,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
+          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3504,7 +3501,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3523,10 +3519,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543603</v>
+        <v>129543344</v>
       </c>
       <c r="B29" t="n">
-        <v>57896</v>
+        <v>57733</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3534,26 +3530,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -3561,7 +3557,11 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571376</v>
+        <v>571283</v>
       </c>
       <c r="R29" t="n">
-        <v>6465679</v>
+        <v>6465682</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
+          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -2249,38 +2249,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543392</v>
+        <v>129543676</v>
       </c>
       <c r="B17" t="n">
-        <v>98780</v>
+        <v>91599</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2288,10 +2287,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571309</v>
+        <v>571480</v>
       </c>
       <c r="R17" t="n">
-        <v>6465740</v>
+        <v>6465733</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2324,11 +2323,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2356,38 +2350,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543383</v>
+        <v>129543452</v>
       </c>
       <c r="B18" t="n">
-        <v>105846</v>
+        <v>92241</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>5454</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2395,10 +2388,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571325</v>
+        <v>571381</v>
       </c>
       <c r="R18" t="n">
-        <v>6465727</v>
+        <v>6465712</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2431,11 +2424,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2463,37 +2451,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129543676</v>
+        <v>129543392</v>
       </c>
       <c r="B19" t="n">
-        <v>91599</v>
+        <v>98780</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2501,10 +2490,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571480</v>
+        <v>571309</v>
       </c>
       <c r="R19" t="n">
-        <v>6465733</v>
+        <v>6465740</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2537,6 +2526,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2564,37 +2558,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129543452</v>
+        <v>129543383</v>
       </c>
       <c r="B20" t="n">
-        <v>92241</v>
+        <v>105846</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5454</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2602,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571381</v>
+        <v>571325</v>
       </c>
       <c r="R20" t="n">
-        <v>6465712</v>
+        <v>6465727</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,6 +2633,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -1001,7 +1001,7 @@
         <v>129543469</v>
       </c>
       <c r="B5" t="n">
-        <v>96222</v>
+        <v>96232</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543544</v>
+        <v>129543327</v>
       </c>
       <c r="B6" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571456</v>
+        <v>571291</v>
       </c>
       <c r="R6" t="n">
-        <v>6465730</v>
+        <v>6465665</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543327</v>
+        <v>129543544</v>
       </c>
       <c r="B7" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571291</v>
+        <v>571456</v>
       </c>
       <c r="R7" t="n">
-        <v>6465665</v>
+        <v>6465730</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,37 +1314,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543463</v>
+        <v>129543522</v>
       </c>
       <c r="B8" t="n">
-        <v>79700</v>
+        <v>98790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1352,10 +1353,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571341</v>
+        <v>571382</v>
       </c>
       <c r="R8" t="n">
-        <v>6465672</v>
+        <v>6465758</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1389,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,39 +1421,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543448</v>
+        <v>129543430</v>
       </c>
       <c r="B9" t="n">
-        <v>4773</v>
+        <v>98790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1455,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571395</v>
+        <v>571367</v>
       </c>
       <c r="R9" t="n">
-        <v>6465767</v>
+        <v>6465787</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,6 +1496,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1518,38 +1528,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129543430</v>
+        <v>129543463</v>
       </c>
       <c r="B10" t="n">
-        <v>98780</v>
+        <v>79700</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1557,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571367</v>
+        <v>571341</v>
       </c>
       <c r="R10" t="n">
-        <v>6465787</v>
+        <v>6465672</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,11 +1602,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1625,38 +1629,39 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543522</v>
+        <v>129543448</v>
       </c>
       <c r="B11" t="n">
-        <v>98780</v>
+        <v>4773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1664,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571382</v>
+        <v>571395</v>
       </c>
       <c r="R11" t="n">
-        <v>6465758</v>
+        <v>6465767</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,11 +1705,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1732,10 +1732,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129543434</v>
+        <v>129543553</v>
       </c>
       <c r="B12" t="n">
-        <v>91599</v>
+        <v>91613</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1743,21 +1743,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>571376</v>
+        <v>571453</v>
       </c>
       <c r="R12" t="n">
-        <v>6465781</v>
+        <v>6465695</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,10 +1833,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129543553</v>
+        <v>129543434</v>
       </c>
       <c r="B13" t="n">
-        <v>91613</v>
+        <v>91599</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,21 +1844,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>571453</v>
+        <v>571376</v>
       </c>
       <c r="R13" t="n">
-        <v>6465695</v>
+        <v>6465781</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,7 +1937,7 @@
         <v>129543516</v>
       </c>
       <c r="B14" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>129543475</v>
       </c>
       <c r="B15" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,10 +2249,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543676</v>
+        <v>129543452</v>
       </c>
       <c r="B17" t="n">
-        <v>91599</v>
+        <v>92241</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2260,21 +2260,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5454</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571480</v>
+        <v>571381</v>
       </c>
       <c r="R17" t="n">
-        <v>6465733</v>
+        <v>6465712</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543452</v>
+        <v>129543676</v>
       </c>
       <c r="B18" t="n">
-        <v>92241</v>
+        <v>91599</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,21 +2361,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5454</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571381</v>
+        <v>571480</v>
       </c>
       <c r="R18" t="n">
-        <v>6465712</v>
+        <v>6465733</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2454,7 +2454,7 @@
         <v>129543392</v>
       </c>
       <c r="B19" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>129543383</v>
       </c>
       <c r="B20" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129543526</v>
       </c>
       <c r="B22" t="n">
-        <v>105846</v>
+        <v>105856</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>129543484</v>
       </c>
       <c r="B24" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>129543348</v>
       </c>
       <c r="B25" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>129543378</v>
       </c>
       <c r="B26" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3295,37 +3295,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543509</v>
+        <v>129543344</v>
       </c>
       <c r="B27" t="n">
-        <v>92052</v>
+        <v>57733</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3333,10 +3350,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571359</v>
+        <v>571283</v>
       </c>
       <c r="R27" t="n">
-        <v>6465750</v>
+        <v>6465682</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3373,7 +3390,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
+          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3382,7 +3399,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3519,54 +3535,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543344</v>
+        <v>129543537</v>
       </c>
       <c r="B29" t="n">
-        <v>57733</v>
+        <v>98790</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571283</v>
+        <v>571452</v>
       </c>
       <c r="R29" t="n">
-        <v>6465682</v>
+        <v>6465730</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3623,6 +3623,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3641,10 +3642,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543537</v>
+        <v>129543509</v>
       </c>
       <c r="B30" t="n">
-        <v>98780</v>
+        <v>92052</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3652,27 +3653,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571452</v>
+        <v>571359</v>
       </c>
       <c r="R30" t="n">
-        <v>6465730</v>
+        <v>6465750</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3748,38 +3748,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129543678</v>
+        <v>129543655</v>
       </c>
       <c r="B31" t="n">
-        <v>98780</v>
+        <v>79700</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3787,10 +3786,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571480</v>
+        <v>571375</v>
       </c>
       <c r="R31" t="n">
-        <v>6465780</v>
+        <v>6465649</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3823,11 +3822,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,10 +3849,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543442</v>
+        <v>129543678</v>
       </c>
       <c r="B32" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3894,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571390</v>
+        <v>571480</v>
       </c>
       <c r="R32" t="n">
-        <v>6465781</v>
+        <v>6465780</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3962,37 +3956,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543655</v>
+        <v>129543442</v>
       </c>
       <c r="B33" t="n">
-        <v>79700</v>
+        <v>98790</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4000,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571375</v>
+        <v>571390</v>
       </c>
       <c r="R33" t="n">
-        <v>6465649</v>
+        <v>6465781</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4036,6 +4031,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4066,7 +4066,7 @@
         <v>129543686</v>
       </c>
       <c r="B34" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>129543389</v>
       </c>
       <c r="B35" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>129543685</v>
       </c>
       <c r="B36" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>129543368</v>
       </c>
       <c r="B37" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4592,38 +4592,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543361</v>
+        <v>129543651</v>
       </c>
       <c r="B39" t="n">
-        <v>98780</v>
+        <v>79700</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4631,10 +4630,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571328</v>
+        <v>571336</v>
       </c>
       <c r="R39" t="n">
-        <v>6465727</v>
+        <v>6465638</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4667,11 +4666,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4702,7 +4696,7 @@
         <v>129543356</v>
       </c>
       <c r="B40" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4806,10 +4800,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543624</v>
+        <v>129543361</v>
       </c>
       <c r="B41" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4845,10 +4839,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571370</v>
+        <v>571328</v>
       </c>
       <c r="R41" t="n">
-        <v>6465662</v>
+        <v>6465727</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4885,7 +4879,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ett tiotal</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4913,37 +4907,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543651</v>
+        <v>129543624</v>
       </c>
       <c r="B42" t="n">
-        <v>79700</v>
+        <v>98790</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4951,10 +4946,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571336</v>
+        <v>571370</v>
       </c>
       <c r="R42" t="n">
-        <v>6465638</v>
+        <v>6465662</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4987,6 +4982,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5118,7 +5118,7 @@
         <v>129543395</v>
       </c>
       <c r="B44" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129543469</v>
+        <v>129543327</v>
       </c>
       <c r="B5" t="n">
-        <v>96232</v>
+        <v>98790</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571323</v>
+        <v>571291</v>
       </c>
       <c r="R5" t="n">
-        <v>6465679</v>
+        <v>6465665</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,6 +1073,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,7 +1105,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543327</v>
+        <v>129543544</v>
       </c>
       <c r="B6" t="n">
         <v>98790</v>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571291</v>
+        <v>571456</v>
       </c>
       <c r="R6" t="n">
-        <v>6465665</v>
+        <v>6465730</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,32 +1212,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543544</v>
+        <v>129543469</v>
       </c>
       <c r="B7" t="n">
-        <v>98790</v>
+        <v>96232</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1246,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571456</v>
+        <v>571323</v>
       </c>
       <c r="R7" t="n">
-        <v>6465730</v>
+        <v>6465679</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,11 +1287,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1314,38 +1314,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543522</v>
+        <v>129543463</v>
       </c>
       <c r="B8" t="n">
-        <v>98790</v>
+        <v>79700</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1353,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571382</v>
+        <v>571341</v>
       </c>
       <c r="R8" t="n">
-        <v>6465758</v>
+        <v>6465672</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,38 +1415,39 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543430</v>
+        <v>129543448</v>
       </c>
       <c r="B9" t="n">
-        <v>98790</v>
+        <v>4773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1460,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571367</v>
+        <v>571395</v>
       </c>
       <c r="R9" t="n">
-        <v>6465787</v>
+        <v>6465767</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,11 +1491,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,37 +1518,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129543463</v>
+        <v>129543522</v>
       </c>
       <c r="B10" t="n">
-        <v>79700</v>
+        <v>98790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1566,10 +1557,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>571341</v>
+        <v>571382</v>
       </c>
       <c r="R10" t="n">
-        <v>6465672</v>
+        <v>6465758</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,6 +1593,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,39 +1625,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129543448</v>
+        <v>129543430</v>
       </c>
       <c r="B11" t="n">
-        <v>4773</v>
+        <v>98790</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1669,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>571395</v>
+        <v>571367</v>
       </c>
       <c r="R11" t="n">
-        <v>6465767</v>
+        <v>6465787</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,6 +1700,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2249,37 +2249,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543452</v>
+        <v>129543383</v>
       </c>
       <c r="B17" t="n">
-        <v>92241</v>
+        <v>105856</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5454</v>
+        <v>221144</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2287,10 +2288,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571381</v>
+        <v>571325</v>
       </c>
       <c r="R17" t="n">
-        <v>6465712</v>
+        <v>6465727</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2323,6 +2324,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2350,10 +2356,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543676</v>
+        <v>129543452</v>
       </c>
       <c r="B18" t="n">
-        <v>91599</v>
+        <v>92241</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,21 +2367,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>5454</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2388,10 +2394,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571480</v>
+        <v>571381</v>
       </c>
       <c r="R18" t="n">
-        <v>6465733</v>
+        <v>6465712</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2451,38 +2457,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129543392</v>
+        <v>129543676</v>
       </c>
       <c r="B19" t="n">
-        <v>98790</v>
+        <v>91599</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2490,10 +2495,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571309</v>
+        <v>571480</v>
       </c>
       <c r="R19" t="n">
-        <v>6465740</v>
+        <v>6465733</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2526,11 +2531,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2558,32 +2558,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129543383</v>
+        <v>129543392</v>
       </c>
       <c r="B20" t="n">
-        <v>105856</v>
+        <v>98790</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571325</v>
+        <v>571309</v>
       </c>
       <c r="R20" t="n">
-        <v>6465727</v>
+        <v>6465740</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ett tjugotal</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3748,37 +3748,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129543655</v>
+        <v>129543678</v>
       </c>
       <c r="B31" t="n">
-        <v>79700</v>
+        <v>98790</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3786,10 +3787,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571375</v>
+        <v>571480</v>
       </c>
       <c r="R31" t="n">
-        <v>6465649</v>
+        <v>6465780</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3822,6 +3823,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3849,7 +3855,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543678</v>
+        <v>129543442</v>
       </c>
       <c r="B32" t="n">
         <v>98790</v>
@@ -3888,10 +3894,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571480</v>
+        <v>571390</v>
       </c>
       <c r="R32" t="n">
-        <v>6465780</v>
+        <v>6465781</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3956,38 +3962,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543442</v>
+        <v>129543655</v>
       </c>
       <c r="B33" t="n">
-        <v>98790</v>
+        <v>79700</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3995,10 +4000,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571390</v>
+        <v>571375</v>
       </c>
       <c r="R33" t="n">
-        <v>6465781</v>
+        <v>6465649</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4031,11 +4036,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -2249,38 +2249,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543383</v>
+        <v>129543452</v>
       </c>
       <c r="B17" t="n">
-        <v>105856</v>
+        <v>92241</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221144</v>
+        <v>5454</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2288,10 +2287,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571325</v>
+        <v>571381</v>
       </c>
       <c r="R17" t="n">
-        <v>6465727</v>
+        <v>6465712</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2324,11 +2323,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2356,37 +2350,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543452</v>
+        <v>129543392</v>
       </c>
       <c r="B18" t="n">
-        <v>92241</v>
+        <v>98790</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5454</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2394,10 +2389,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571381</v>
+        <v>571309</v>
       </c>
       <c r="R18" t="n">
-        <v>6465712</v>
+        <v>6465740</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2430,6 +2425,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2558,32 +2558,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129543392</v>
+        <v>129543383</v>
       </c>
       <c r="B20" t="n">
-        <v>98790</v>
+        <v>105856</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571309</v>
+        <v>571325</v>
       </c>
       <c r="R20" t="n">
-        <v>6465740</v>
+        <v>6465727</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3295,10 +3295,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543344</v>
+        <v>129543603</v>
       </c>
       <c r="B27" t="n">
-        <v>57733</v>
+        <v>57896</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3306,26 +3306,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -3333,11 +3333,7 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -3350,10 +3346,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571283</v>
+        <v>571376</v>
       </c>
       <c r="R27" t="n">
-        <v>6465682</v>
+        <v>6465679</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3390,7 +3386,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
+          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3417,50 +3413,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543603</v>
+        <v>129543509</v>
       </c>
       <c r="B28" t="n">
-        <v>57896</v>
+        <v>92052</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3468,10 +3451,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571376</v>
+        <v>571359</v>
       </c>
       <c r="R28" t="n">
-        <v>6465679</v>
+        <v>6465750</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3508,7 +3491,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
+          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3517,6 +3500,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3535,38 +3519,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543537</v>
+        <v>129543344</v>
       </c>
       <c r="B29" t="n">
-        <v>98790</v>
+        <v>57733</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571452</v>
+        <v>571283</v>
       </c>
       <c r="R29" t="n">
-        <v>6465730</v>
+        <v>6465682</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3623,7 +3623,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3642,10 +3641,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543509</v>
+        <v>129543537</v>
       </c>
       <c r="B30" t="n">
-        <v>92052</v>
+        <v>98790</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3653,26 +3652,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3680,10 +3680,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571359</v>
+        <v>571452</v>
       </c>
       <c r="R30" t="n">
-        <v>6465750</v>
+        <v>6465730</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4491,37 +4491,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129543564</v>
+        <v>129543356</v>
       </c>
       <c r="B38" t="n">
-        <v>91599</v>
+        <v>98790</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4529,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>571443</v>
+        <v>571315</v>
       </c>
       <c r="R38" t="n">
-        <v>6465681</v>
+        <v>6465727</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4565,6 +4566,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4592,37 +4598,38 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543651</v>
+        <v>129543361</v>
       </c>
       <c r="B39" t="n">
-        <v>79700</v>
+        <v>98790</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4630,10 +4637,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571336</v>
+        <v>571328</v>
       </c>
       <c r="R39" t="n">
-        <v>6465638</v>
+        <v>6465727</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4666,6 +4673,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4693,7 +4705,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543356</v>
+        <v>129543624</v>
       </c>
       <c r="B40" t="n">
         <v>98790</v>
@@ -4732,10 +4744,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571315</v>
+        <v>571370</v>
       </c>
       <c r="R40" t="n">
-        <v>6465727</v>
+        <v>6465662</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4772,7 +4784,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4800,38 +4812,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543361</v>
+        <v>129543651</v>
       </c>
       <c r="B41" t="n">
-        <v>98790</v>
+        <v>79700</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4839,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571328</v>
+        <v>571336</v>
       </c>
       <c r="R41" t="n">
-        <v>6465727</v>
+        <v>6465638</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4875,11 +4886,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4907,38 +4913,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543624</v>
+        <v>129543564</v>
       </c>
       <c r="B42" t="n">
-        <v>98790</v>
+        <v>91599</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4946,10 +4951,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571370</v>
+        <v>571443</v>
       </c>
       <c r="R42" t="n">
-        <v>6465662</v>
+        <v>6465681</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4982,11 +4987,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5225,7 +5225,7 @@
         <v>129741149</v>
       </c>
       <c r="B45" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>129741141</v>
       </c>
       <c r="B46" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -998,32 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129543327</v>
+        <v>129543469</v>
       </c>
       <c r="B5" t="n">
-        <v>98790</v>
+        <v>96236</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>571291</v>
+        <v>571323</v>
       </c>
       <c r="R5" t="n">
-        <v>6465665</v>
+        <v>6465679</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,11 +1073,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129543544</v>
+        <v>129543327</v>
       </c>
       <c r="B6" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571456</v>
+        <v>571291</v>
       </c>
       <c r="R6" t="n">
-        <v>6465730</v>
+        <v>6465665</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,32 +1207,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129543469</v>
+        <v>129543544</v>
       </c>
       <c r="B7" t="n">
-        <v>96232</v>
+        <v>98794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571323</v>
+        <v>571456</v>
       </c>
       <c r="R7" t="n">
-        <v>6465679</v>
+        <v>6465730</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,6 +1282,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1314,37 +1314,39 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129543463</v>
+        <v>129543448</v>
       </c>
       <c r="B8" t="n">
-        <v>79700</v>
+        <v>4773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1352,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571341</v>
+        <v>571395</v>
       </c>
       <c r="R8" t="n">
-        <v>6465672</v>
+        <v>6465767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,39 +1417,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129543448</v>
+        <v>129543463</v>
       </c>
       <c r="B9" t="n">
-        <v>4773</v>
+        <v>79703</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>571395</v>
+        <v>571341</v>
       </c>
       <c r="R9" t="n">
-        <v>6465767</v>
+        <v>6465672</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1521,7 +1521,7 @@
         <v>129543522</v>
       </c>
       <c r="B10" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>129543430</v>
       </c>
       <c r="B11" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>129543553</v>
       </c>
       <c r="B12" t="n">
-        <v>91613</v>
+        <v>91616</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>129543434</v>
       </c>
       <c r="B13" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>129543516</v>
       </c>
       <c r="B14" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>129543475</v>
       </c>
       <c r="B15" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>129543571</v>
       </c>
       <c r="B16" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2249,10 +2249,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129543452</v>
+        <v>129543676</v>
       </c>
       <c r="B17" t="n">
-        <v>92241</v>
+        <v>91602</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2260,21 +2260,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5454</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>571381</v>
+        <v>571480</v>
       </c>
       <c r="R17" t="n">
-        <v>6465712</v>
+        <v>6465733</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,38 +2350,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129543392</v>
+        <v>129543452</v>
       </c>
       <c r="B18" t="n">
-        <v>98790</v>
+        <v>92244</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5454</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2389,10 +2388,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>571309</v>
+        <v>571381</v>
       </c>
       <c r="R18" t="n">
-        <v>6465740</v>
+        <v>6465712</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2425,11 +2424,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2457,37 +2451,38 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129543676</v>
+        <v>129543383</v>
       </c>
       <c r="B19" t="n">
-        <v>91599</v>
+        <v>105860</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2495,10 +2490,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>571480</v>
+        <v>571325</v>
       </c>
       <c r="R19" t="n">
-        <v>6465733</v>
+        <v>6465727</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,6 +2526,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ett tjugotal</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2558,32 +2558,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129543383</v>
+        <v>129543392</v>
       </c>
       <c r="B20" t="n">
-        <v>105856</v>
+        <v>98794</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2597,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>571325</v>
+        <v>571309</v>
       </c>
       <c r="R20" t="n">
-        <v>6465727</v>
+        <v>6465740</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ett tjugotal</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2668,7 +2668,7 @@
         <v>129543658</v>
       </c>
       <c r="B21" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>129543526</v>
       </c>
       <c r="B22" t="n">
-        <v>105856</v>
+        <v>105860</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>129543457</v>
       </c>
       <c r="B23" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>129543484</v>
       </c>
       <c r="B24" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>129543348</v>
       </c>
       <c r="B25" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>129543378</v>
       </c>
       <c r="B26" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3295,50 +3295,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129543603</v>
+        <v>129543509</v>
       </c>
       <c r="B27" t="n">
-        <v>57896</v>
+        <v>92055</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3346,10 +3333,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>571376</v>
+        <v>571359</v>
       </c>
       <c r="R27" t="n">
-        <v>6465679</v>
+        <v>6465750</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3386,7 +3373,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
+          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3395,6 +3382,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3413,37 +3401,54 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129543509</v>
+        <v>129543344</v>
       </c>
       <c r="B28" t="n">
-        <v>92052</v>
+        <v>57734</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3451,10 +3456,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>571359</v>
+        <v>571283</v>
       </c>
       <c r="R28" t="n">
-        <v>6465750</v>
+        <v>6465682</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3491,7 +3496,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Relativt ovanligt i Götaland med rynkskinn som är en indikator för urskogsartad skog.</t>
+          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3500,7 +3505,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3519,54 +3523,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129543344</v>
+        <v>129543537</v>
       </c>
       <c r="B29" t="n">
-        <v>57733</v>
+        <v>98794</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3574,10 +3562,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>571283</v>
+        <v>571452</v>
       </c>
       <c r="R29" t="n">
-        <v>6465682</v>
+        <v>6465730</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3614,7 +3602,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Den gamla och på död ved extrem rika naturskogen är en viktig del av spillkråkans revir.</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3623,6 +3611,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3641,38 +3630,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129543537</v>
+        <v>129543603</v>
       </c>
       <c r="B30" t="n">
-        <v>98790</v>
+        <v>57895</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3680,10 +3681,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>571452</v>
+        <v>571376</v>
       </c>
       <c r="R30" t="n">
-        <v>6465730</v>
+        <v>6465679</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3720,7 +3721,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Enstaka</t>
+          <t>Revirparet i sitt permanenta revir dvs. naturskogen är en viktig del av reviret.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3729,7 +3730,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3748,38 +3748,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129543678</v>
+        <v>129543655</v>
       </c>
       <c r="B31" t="n">
-        <v>98790</v>
+        <v>79703</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3787,10 +3786,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>571480</v>
+        <v>571375</v>
       </c>
       <c r="R31" t="n">
-        <v>6465780</v>
+        <v>6465649</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3823,11 +3822,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3855,10 +3849,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129543442</v>
+        <v>129543678</v>
       </c>
       <c r="B32" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3894,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>571390</v>
+        <v>571480</v>
       </c>
       <c r="R32" t="n">
-        <v>6465781</v>
+        <v>6465780</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3962,37 +3956,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129543655</v>
+        <v>129543442</v>
       </c>
       <c r="B33" t="n">
-        <v>79700</v>
+        <v>98794</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4000,10 +3995,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>571375</v>
+        <v>571390</v>
       </c>
       <c r="R33" t="n">
-        <v>6465649</v>
+        <v>6465781</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4036,6 +4031,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4066,7 +4066,7 @@
         <v>129543686</v>
       </c>
       <c r="B34" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>129543389</v>
       </c>
       <c r="B35" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>129543685</v>
       </c>
       <c r="B36" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>129543368</v>
       </c>
       <c r="B37" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4491,38 +4491,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129543356</v>
+        <v>129543564</v>
       </c>
       <c r="B38" t="n">
-        <v>98790</v>
+        <v>91602</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4530,10 +4529,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>571315</v>
+        <v>571443</v>
       </c>
       <c r="R38" t="n">
-        <v>6465727</v>
+        <v>6465681</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,11 +4565,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4598,38 +4592,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129543361</v>
+        <v>129543651</v>
       </c>
       <c r="B39" t="n">
-        <v>98790</v>
+        <v>79703</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4637,10 +4630,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>571328</v>
+        <v>571336</v>
       </c>
       <c r="R39" t="n">
-        <v>6465727</v>
+        <v>6465638</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4673,11 +4666,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4705,10 +4693,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129543624</v>
+        <v>129543356</v>
       </c>
       <c r="B40" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4744,10 +4732,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>571370</v>
+        <v>571315</v>
       </c>
       <c r="R40" t="n">
-        <v>6465662</v>
+        <v>6465727</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4784,7 +4772,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ett tiotal</t>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4812,37 +4800,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129543651</v>
+        <v>129543361</v>
       </c>
       <c r="B41" t="n">
-        <v>79700</v>
+        <v>98794</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4850,10 +4839,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>571336</v>
+        <v>571328</v>
       </c>
       <c r="R41" t="n">
-        <v>6465638</v>
+        <v>6465727</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4886,6 +4875,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Enstaka</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4913,37 +4907,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129543564</v>
+        <v>129543624</v>
       </c>
       <c r="B42" t="n">
-        <v>91599</v>
+        <v>98794</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4951,10 +4946,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>571443</v>
+        <v>571370</v>
       </c>
       <c r="R42" t="n">
-        <v>6465681</v>
+        <v>6465662</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4987,6 +4982,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ett tiotal</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5017,7 +5017,7 @@
         <v>129543662</v>
       </c>
       <c r="B43" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
         <v>129543395</v>
       </c>
       <c r="B44" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -5225,7 +5225,7 @@
         <v>129741149</v>
       </c>
       <c r="B45" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>129741141</v>
       </c>
       <c r="B46" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -3404,7 +3404,7 @@
         <v>129543344</v>
       </c>
       <c r="B28" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -5225,7 +5225,7 @@
         <v>129741149</v>
       </c>
       <c r="B45" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 46984-2025 artfynd.xlsx
+++ b/artfynd/A 46984-2025 artfynd.xlsx
@@ -3404,7 +3404,7 @@
         <v>129543344</v>
       </c>
       <c r="B28" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>129741141</v>
       </c>
       <c r="B46" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
